--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zhen\Desktop\paper-monitor-v12.0\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zhen\Desktop\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD68328-3D10-4DE3-975A-881875AE182F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC074C08-1459-419F-8A0E-470F374AC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="7368" yWindow="2352" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="552">
   <si>
     <t>Category</t>
   </si>
@@ -604,9 +604,6 @@
     <t>1366-5545</t>
   </si>
   <si>
-    <t>2194-5179</t>
-  </si>
-  <si>
     <t>0261-5177</t>
   </si>
   <si>
@@ -799,9 +796,6 @@
     <t>1545-8490</t>
   </si>
   <si>
-    <t>2767-1054</t>
-  </si>
-  <si>
     <t>1059-1478</t>
   </si>
   <si>
@@ -1006,9 +1000,6 @@
     <t>1878-5794</t>
   </si>
   <si>
-    <t>2194-5187</t>
-  </si>
-  <si>
     <t>1879-3193</t>
   </si>
   <si>
@@ -1174,9 +1165,6 @@
     <t>1545-8504</t>
   </si>
   <si>
-    <t>2767-1062</t>
-  </si>
-  <si>
     <t>1937-5956</t>
   </si>
   <si>
@@ -1679,6 +1667,15 @@
   </si>
   <si>
     <t>crossref</t>
+  </si>
+  <si>
+    <t>2691-4581</t>
+  </si>
+  <si>
+    <t>2193-9446</t>
+  </si>
+  <si>
+    <t>2694-4022</t>
   </si>
 </sst>
 </file>
@@ -2118,13 +2115,13 @@
         <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="I2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2141,13 +2138,13 @@
         <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="I3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2164,13 +2161,13 @@
         <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="I4" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2187,13 +2184,13 @@
         <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="I5" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2210,13 +2207,13 @@
         <v>158</v>
       </c>
       <c r="E6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="I6" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2233,13 +2230,13 @@
         <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I7" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2256,13 +2253,13 @@
         <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="I8" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2279,13 +2276,13 @@
         <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="I9" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2302,13 +2299,13 @@
         <v>162</v>
       </c>
       <c r="E10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="I10" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2325,13 +2322,13 @@
         <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I11" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2348,13 +2345,13 @@
         <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="I12" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2371,13 +2368,13 @@
         <v>165</v>
       </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I13" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2394,13 +2391,13 @@
         <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="I14" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2417,13 +2414,13 @@
         <v>167</v>
       </c>
       <c r="E15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="I15" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2443,10 +2440,10 @@
         <v>168</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I16" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2463,13 +2460,13 @@
         <v>169</v>
       </c>
       <c r="E17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="I17" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2486,13 +2483,13 @@
         <v>170</v>
       </c>
       <c r="E18" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="I18" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2509,13 +2506,13 @@
         <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="I19" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2532,13 +2529,13 @@
         <v>172</v>
       </c>
       <c r="E20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="I20" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2555,13 +2552,13 @@
         <v>173</v>
       </c>
       <c r="E21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I21" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2578,13 +2575,13 @@
         <v>174</v>
       </c>
       <c r="E22" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I22" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2601,13 +2598,13 @@
         <v>175</v>
       </c>
       <c r="E23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="I23" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2624,13 +2621,13 @@
         <v>176</v>
       </c>
       <c r="E24" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="I24" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2647,13 +2644,13 @@
         <v>177</v>
       </c>
       <c r="E25" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="I25" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2670,13 +2667,13 @@
         <v>178</v>
       </c>
       <c r="E26" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="I26" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2693,13 +2690,13 @@
         <v>179</v>
       </c>
       <c r="E27" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="I27" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2719,10 +2716,10 @@
         <v>180</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="I28" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2739,13 +2736,13 @@
         <v>181</v>
       </c>
       <c r="E29" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="I29" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2762,13 +2759,13 @@
         <v>182</v>
       </c>
       <c r="E30" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="I30" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2785,13 +2782,13 @@
         <v>183</v>
       </c>
       <c r="E31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="I31" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2808,13 +2805,13 @@
         <v>184</v>
       </c>
       <c r="E32" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="I32" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2831,13 +2828,13 @@
         <v>185</v>
       </c>
       <c r="E33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="I33" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2854,13 +2851,13 @@
         <v>186</v>
       </c>
       <c r="E34" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="I34" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2877,13 +2874,13 @@
         <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="I35" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2900,13 +2897,13 @@
         <v>188</v>
       </c>
       <c r="E36" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I36" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2923,13 +2920,13 @@
         <v>189</v>
       </c>
       <c r="E37" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="I37" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2946,13 +2943,13 @@
         <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="I38" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2969,13 +2966,13 @@
         <v>191</v>
       </c>
       <c r="E39" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="I39" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2992,13 +2989,13 @@
         <v>192</v>
       </c>
       <c r="E40" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="I40" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3015,13 +3012,13 @@
         <v>193</v>
       </c>
       <c r="E41" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="I41" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3035,16 +3032,13 @@
         <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>194</v>
-      </c>
-      <c r="E42" t="s">
-        <v>328</v>
+        <v>550</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="I42" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3058,16 +3052,16 @@
         <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="I43" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3081,16 +3075,16 @@
         <v>59</v>
       </c>
       <c r="D44" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="I44" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3104,16 +3098,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="I45" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3127,16 +3121,16 @@
         <v>61</v>
       </c>
       <c r="D46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E46" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="I46" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3150,16 +3144,16 @@
         <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E47" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="I47" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3173,16 +3167,16 @@
         <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="I48" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3196,16 +3190,16 @@
         <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="I49" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3219,16 +3213,16 @@
         <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E50" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="I50" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3242,16 +3236,16 @@
         <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="I51" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3265,16 +3259,16 @@
         <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E52" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="I52" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3288,16 +3282,16 @@
         <v>68</v>
       </c>
       <c r="D53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E53" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="I53" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3311,16 +3305,16 @@
         <v>69</v>
       </c>
       <c r="D54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E54" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="I54" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3334,16 +3328,16 @@
         <v>70</v>
       </c>
       <c r="D55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E55" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="I55" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3357,16 +3351,16 @@
         <v>71</v>
       </c>
       <c r="D56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E56" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="I56" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3380,16 +3374,16 @@
         <v>72</v>
       </c>
       <c r="D57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E57" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="I57" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3403,16 +3397,16 @@
         <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E58" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="I58" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3426,16 +3420,16 @@
         <v>74</v>
       </c>
       <c r="D59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E59" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="I59" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3449,16 +3443,16 @@
         <v>75</v>
       </c>
       <c r="D60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E60" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I60" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3472,16 +3466,16 @@
         <v>76</v>
       </c>
       <c r="D61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E61" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="I61" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3495,16 +3489,16 @@
         <v>77</v>
       </c>
       <c r="D62" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E62" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I62" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3518,16 +3512,16 @@
         <v>78</v>
       </c>
       <c r="D63" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E63" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="I63" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3541,16 +3535,16 @@
         <v>79</v>
       </c>
       <c r="D64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E64" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I64" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3564,16 +3558,16 @@
         <v>80</v>
       </c>
       <c r="D65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E65" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="I65" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3587,16 +3581,16 @@
         <v>81</v>
       </c>
       <c r="D66" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E66" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I66" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3610,16 +3604,16 @@
         <v>82</v>
       </c>
       <c r="D67" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E67" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="I67" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3633,16 +3627,16 @@
         <v>83</v>
       </c>
       <c r="D68" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E68" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="I68" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3656,16 +3650,16 @@
         <v>84</v>
       </c>
       <c r="D69" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E69" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="I69" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3679,16 +3673,16 @@
         <v>85</v>
       </c>
       <c r="D70" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E70" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I70" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3702,16 +3696,16 @@
         <v>86</v>
       </c>
       <c r="D71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E71" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="I71" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3725,16 +3719,16 @@
         <v>87</v>
       </c>
       <c r="D72" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E72" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="I72" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3748,16 +3742,16 @@
         <v>88</v>
       </c>
       <c r="D73" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E73" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="I73" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3771,16 +3765,16 @@
         <v>89</v>
       </c>
       <c r="D74" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E74" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="I74" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3794,16 +3788,16 @@
         <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E75" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="I75" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3817,16 +3811,16 @@
         <v>91</v>
       </c>
       <c r="D76" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E76" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="I76" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3840,16 +3834,16 @@
         <v>92</v>
       </c>
       <c r="D77" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E77" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="I77" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3863,16 +3857,16 @@
         <v>93</v>
       </c>
       <c r="D78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="I78" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3886,16 +3880,16 @@
         <v>94</v>
       </c>
       <c r="D79" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E79" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="I79" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3909,16 +3903,16 @@
         <v>95</v>
       </c>
       <c r="D80" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E80" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="I80" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3932,16 +3926,16 @@
         <v>96</v>
       </c>
       <c r="D81" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E81" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="I81" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3955,16 +3949,16 @@
         <v>97</v>
       </c>
       <c r="D82" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E82" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="I82" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3978,16 +3972,16 @@
         <v>98</v>
       </c>
       <c r="D83" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E83" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="I83" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4001,16 +3995,16 @@
         <v>99</v>
       </c>
       <c r="D84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="I84" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4024,16 +4018,16 @@
         <v>100</v>
       </c>
       <c r="D85" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E85" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="I85" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4047,16 +4041,16 @@
         <v>101</v>
       </c>
       <c r="D86" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E86" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I86" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4070,16 +4064,16 @@
         <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E87" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I87" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4093,16 +4087,16 @@
         <v>103</v>
       </c>
       <c r="D88" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E88" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="I88" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4116,16 +4110,16 @@
         <v>104</v>
       </c>
       <c r="D89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E89" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="I89" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4139,16 +4133,16 @@
         <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="I90" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4162,16 +4156,16 @@
         <v>106</v>
       </c>
       <c r="D91" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E91" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="I91" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4185,16 +4179,16 @@
         <v>107</v>
       </c>
       <c r="D92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E92" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="I92" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4208,16 +4202,16 @@
         <v>108</v>
       </c>
       <c r="D93" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E93" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="I93" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4231,16 +4225,16 @@
         <v>109</v>
       </c>
       <c r="D94" t="s">
-        <v>245</v>
+        <v>549</v>
       </c>
       <c r="E94" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="I94" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4254,16 +4248,16 @@
         <v>110</v>
       </c>
       <c r="D95" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E95" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="I95" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4277,16 +4271,16 @@
         <v>111</v>
       </c>
       <c r="D96" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E96" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="I96" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4300,16 +4294,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E97" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="I97" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4323,16 +4317,16 @@
         <v>113</v>
       </c>
       <c r="D98" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E98" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="I98" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4346,16 +4340,16 @@
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E99" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="I99" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4369,16 +4363,16 @@
         <v>115</v>
       </c>
       <c r="D100" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E100" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I100" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4392,16 +4386,16 @@
         <v>116</v>
       </c>
       <c r="D101" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E101" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="I101" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4415,16 +4409,16 @@
         <v>117</v>
       </c>
       <c r="D102" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E102" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I102" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4438,16 +4432,16 @@
         <v>118</v>
       </c>
       <c r="D103" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E103" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="I103" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4461,16 +4455,16 @@
         <v>119</v>
       </c>
       <c r="D104" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E104" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I104" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4484,16 +4478,16 @@
         <v>120</v>
       </c>
       <c r="D105" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E105" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="I105" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4507,16 +4501,16 @@
         <v>121</v>
       </c>
       <c r="D106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E106" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="I106" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4530,16 +4524,16 @@
         <v>122</v>
       </c>
       <c r="D107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E107" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="I107" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4553,16 +4547,13 @@
         <v>123</v>
       </c>
       <c r="D108" t="s">
-        <v>259</v>
-      </c>
-      <c r="E108" t="s">
-        <v>384</v>
+        <v>551</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="I108" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4576,16 +4567,16 @@
         <v>124</v>
       </c>
       <c r="D109" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E109" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="I109" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4599,16 +4590,16 @@
         <v>125</v>
       </c>
       <c r="D110" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E110" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="I110" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4622,16 +4613,16 @@
         <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E111" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I111" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4645,16 +4636,16 @@
         <v>127</v>
       </c>
       <c r="D112" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E112" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="I112" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4668,16 +4659,16 @@
         <v>128</v>
       </c>
       <c r="D113" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E113" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I113" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4691,16 +4682,16 @@
         <v>129</v>
       </c>
       <c r="D114" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E114" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="I114" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4714,16 +4705,16 @@
         <v>130</v>
       </c>
       <c r="D115" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E115" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="I115" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4737,16 +4728,16 @@
         <v>131</v>
       </c>
       <c r="D116" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E116" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="I116" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4760,16 +4751,16 @@
         <v>132</v>
       </c>
       <c r="D117" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E117" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="I117" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4783,16 +4774,16 @@
         <v>133</v>
       </c>
       <c r="D118" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E118" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I118" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4806,16 +4797,16 @@
         <v>134</v>
       </c>
       <c r="D119" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E119" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="I119" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4829,16 +4820,16 @@
         <v>135</v>
       </c>
       <c r="D120" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E120" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I120" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4852,16 +4843,16 @@
         <v>136</v>
       </c>
       <c r="D121" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E121" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I121" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4875,16 +4866,16 @@
         <v>137</v>
       </c>
       <c r="D122" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E122" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="I122" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4898,16 +4889,16 @@
         <v>138</v>
       </c>
       <c r="D123" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E123" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="I123" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4921,16 +4912,16 @@
         <v>139</v>
       </c>
       <c r="D124" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E124" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="I124" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4944,16 +4935,16 @@
         <v>140</v>
       </c>
       <c r="D125" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E125" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="I125" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4967,16 +4958,16 @@
         <v>141</v>
       </c>
       <c r="D126" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E126" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="I126" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4990,16 +4981,16 @@
         <v>142</v>
       </c>
       <c r="D127" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E127" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="I127" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5013,16 +5004,16 @@
         <v>143</v>
       </c>
       <c r="D128" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E128" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="I128" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5036,16 +5027,16 @@
         <v>144</v>
       </c>
       <c r="D129" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E129" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="I129" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5059,16 +5050,16 @@
         <v>145</v>
       </c>
       <c r="D130" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E130" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="I130" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5082,16 +5073,16 @@
         <v>146</v>
       </c>
       <c r="D131" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E131" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I131" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5105,16 +5096,16 @@
         <v>147</v>
       </c>
       <c r="D132" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E132" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I132" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5128,16 +5119,16 @@
         <v>148</v>
       </c>
       <c r="D133" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E133" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="I133" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5151,16 +5142,16 @@
         <v>149</v>
       </c>
       <c r="D134" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E134" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="I134" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5174,16 +5165,16 @@
         <v>150</v>
       </c>
       <c r="D135" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E135" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="I135" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5197,16 +5188,16 @@
         <v>151</v>
       </c>
       <c r="D136" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E136" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="I136" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5220,16 +5211,16 @@
         <v>152</v>
       </c>
       <c r="D137" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E137" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I137" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5243,16 +5234,16 @@
         <v>153</v>
       </c>
       <c r="D138" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E138" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="I138" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>

--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zhen\Desktop\paper-monitor\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my files\onedrive\cv\dm-dut.github.io\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC074C08-1459-419F-8A0E-470F374AC908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74912D0F-96C7-4D6B-A266-17B29D407061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1584" yWindow="2424" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="553">
   <si>
     <t>Category</t>
   </si>
@@ -184,9 +184,6 @@
     <t>Journal of Retailing and Consumer Services</t>
   </si>
   <si>
-    <t>Transportation Research, Series B: Methodological</t>
-  </si>
-  <si>
     <t>Transportation Research, Part D: Transport and Environment</t>
   </si>
   <si>
@@ -1676,6 +1673,14 @@
   </si>
   <si>
     <t>2694-4022</t>
+  </si>
+  <si>
+    <t>1389-5753</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transportation Research, Part B: Methodological</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2112,16 +2117,16 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2135,16 +2140,16 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2158,16 +2163,16 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2181,16 +2186,16 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2204,16 +2209,16 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2227,16 +2232,16 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2250,16 +2255,16 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2273,16 +2278,16 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2296,16 +2301,16 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2319,16 +2324,16 @@
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I11" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2342,16 +2347,16 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2365,16 +2370,16 @@
         <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I13" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2388,16 +2393,16 @@
         <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2411,16 +2416,16 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.3">
@@ -2434,16 +2439,16 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I16" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2457,16 +2462,16 @@
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I17" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2480,16 +2485,16 @@
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I18" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2503,16 +2508,16 @@
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I19" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2526,16 +2531,16 @@
         <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I20" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2549,16 +2554,16 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I21" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2572,16 +2577,16 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I22" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2595,16 +2600,16 @@
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I23" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2618,16 +2623,16 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I24" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2641,16 +2646,16 @@
         <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E25" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2664,16 +2669,16 @@
         <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I26" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2687,16 +2692,16 @@
         <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I27" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2710,16 +2715,16 @@
         <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I28" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2733,16 +2738,16 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I29" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2756,16 +2761,16 @@
         <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I30" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2779,16 +2784,16 @@
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I31" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2802,16 +2807,16 @@
         <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I32" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2825,16 +2830,16 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I33" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2848,16 +2853,16 @@
         <v>49</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I34" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2871,16 +2876,16 @@
         <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I35" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2894,16 +2899,16 @@
         <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I36" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2917,16 +2922,16 @@
         <v>52</v>
       </c>
       <c r="D37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E37" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I37" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2940,16 +2945,16 @@
         <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I38" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2960,19 +2965,19 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>552</v>
       </c>
       <c r="D39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E39" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I39" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -2983,19 +2988,19 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I40" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3006,19 +3011,19 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I41" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3029,16 +3034,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I42" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3049,19 +3054,19 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I43" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3072,19 +3077,19 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I44" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3095,19 +3100,19 @@
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I45" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3118,19 +3123,19 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E46" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I46" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3141,19 +3146,19 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E47" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I47" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3164,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I48" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3187,19 +3192,19 @@
         <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E49" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I49" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3210,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E50" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3233,19 +3238,19 @@
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E51" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I51" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3256,19 +3261,19 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D52" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E52" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I52" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3279,19 +3284,19 @@
         <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E53" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I53" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3302,19 +3307,19 @@
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E54" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I54" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3325,19 +3330,19 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E55" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I55" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3348,19 +3353,19 @@
         <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E56" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I56" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3371,19 +3376,19 @@
         <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E57" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I57" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3394,19 +3399,19 @@
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E58" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I58" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3417,19 +3422,19 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E59" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I59" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3440,19 +3445,19 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I60" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3463,19 +3468,19 @@
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E61" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I61" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3486,19 +3491,19 @@
         <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E62" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I62" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3509,19 +3514,19 @@
         <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E63" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I63" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3532,19 +3537,19 @@
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E64" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I64" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3555,19 +3560,19 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I65" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3578,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E66" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I66" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3601,19 +3606,19 @@
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E67" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I67" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3624,19 +3629,19 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E68" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I68" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3647,19 +3652,19 @@
         <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D69" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E69" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I69" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3670,19 +3675,19 @@
         <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E70" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I70" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3693,19 +3698,19 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E71" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I71" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3716,19 +3721,19 @@
         <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E72" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I72" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3739,19 +3744,19 @@
         <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D73" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E73" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I73" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3762,19 +3767,19 @@
         <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E74" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I74" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3785,19 +3790,19 @@
         <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D75" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E75" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I75" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3808,19 +3813,19 @@
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E76" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I76" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3831,19 +3836,19 @@
         <v>19</v>
       </c>
       <c r="C77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E77" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I77" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3854,19 +3859,19 @@
         <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
-        <v>229</v>
+        <v>551</v>
       </c>
       <c r="E78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I78" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3877,19 +3882,19 @@
         <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E79" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I79" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3900,19 +3905,19 @@
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E80" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I80" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3923,19 +3928,19 @@
         <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I81" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3946,19 +3951,19 @@
         <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E82" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I82" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3969,19 +3974,19 @@
         <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E83" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I83" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3992,19 +3997,19 @@
         <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D84" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E84" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I84" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4015,19 +4020,19 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D85" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E85" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I85" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4038,19 +4043,19 @@
         <v>30</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E86" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I86" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4061,19 +4066,19 @@
         <v>31</v>
       </c>
       <c r="C87" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D87" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E87" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I87" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4084,19 +4089,19 @@
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E88" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I88" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4107,19 +4112,19 @@
         <v>2</v>
       </c>
       <c r="C89" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E89" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I89" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4130,19 +4135,19 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I90" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4153,19 +4158,19 @@
         <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E91" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I91" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4176,19 +4181,19 @@
         <v>5</v>
       </c>
       <c r="C92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E92" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I92" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4199,19 +4204,19 @@
         <v>6</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E93" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I93" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4222,19 +4227,19 @@
         <v>7</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D94" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E94" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I94" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4245,19 +4250,19 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D95" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E95" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I95" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4268,19 +4273,19 @@
         <v>9</v>
       </c>
       <c r="C96" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E96" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I96" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4291,19 +4296,19 @@
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E97" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I97" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4314,19 +4319,19 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E98" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I98" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4337,19 +4342,19 @@
         <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D99" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E99" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I99" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4360,19 +4365,19 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I100" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4383,19 +4388,19 @@
         <v>15</v>
       </c>
       <c r="C101" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D101" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E101" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I101" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4406,19 +4411,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E102" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I102" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4429,19 +4434,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D103" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E103" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I103" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4452,19 +4457,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D104" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E104" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I104" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4475,19 +4480,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E105" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I105" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4498,19 +4503,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E106" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I106" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4521,19 +4526,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D107" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I107" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4544,16 +4549,16 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I108" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4564,19 +4569,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E109" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I109" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4587,19 +4592,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D110" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E110" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I110" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4610,19 +4615,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D111" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E111" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I111" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4633,19 +4638,19 @@
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E112" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I112" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4656,19 +4661,19 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D113" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E113" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I113" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4679,19 +4684,19 @@
         <v>15</v>
       </c>
       <c r="C114" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D114" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E114" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I114" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4702,19 +4707,19 @@
         <v>1</v>
       </c>
       <c r="C115" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D115" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E115" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I115" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4725,19 +4730,19 @@
         <v>2</v>
       </c>
       <c r="C116" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D116" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E116" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I116" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4748,19 +4753,19 @@
         <v>3</v>
       </c>
       <c r="C117" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D117" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E117" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I117" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4771,19 +4776,19 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D118" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E118" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I118" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4794,19 +4799,19 @@
         <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E119" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I119" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4817,19 +4822,19 @@
         <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D120" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E120" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I120" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4840,19 +4845,19 @@
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E121" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I121" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4863,19 +4868,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D122" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E122" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I122" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4886,19 +4891,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D123" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E123" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I123" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4909,19 +4914,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D124" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E124" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I124" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4932,19 +4937,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E125" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I125" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4955,19 +4960,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D126" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E126" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -4978,19 +4983,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E127" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I127" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5001,19 +5006,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D128" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I128" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5024,19 +5029,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E129" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I129" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5047,19 +5052,19 @@
         <v>10</v>
       </c>
       <c r="C130" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E130" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I130" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5070,19 +5075,19 @@
         <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D131" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E131" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I131" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5093,19 +5098,19 @@
         <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D132" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E132" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I132" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5116,19 +5121,19 @@
         <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D133" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E133" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I133" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5139,19 +5144,19 @@
         <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D134" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E134" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I134" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5162,19 +5167,19 @@
         <v>15</v>
       </c>
       <c r="C135" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D135" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E135" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I135" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5185,19 +5190,19 @@
         <v>16</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D136" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E136" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I136" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5208,19 +5213,19 @@
         <v>17</v>
       </c>
       <c r="C137" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D137" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E137" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I137" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -5231,19 +5236,19 @@
         <v>18</v>
       </c>
       <c r="C138" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D138" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E138" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I138" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my files\onedrive\cv\dm-dut.github.io\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74912D0F-96C7-4D6B-A266-17B29D407061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC535E6-2FB8-4DEE-A069-CA064BA3C879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1584" yWindow="2424" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="556">
   <si>
     <t>Category</t>
   </si>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>Artificial Intelligence Review</t>
-  </si>
-  <si>
-    <t>Frontiers of Engineering Management</t>
   </si>
   <si>
     <t>Journal of Systems Science and Systems Engineering</t>
@@ -1680,6 +1677,21 @@
   </si>
   <si>
     <t>Transportation Research, Part B: Methodological</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transportation Research Part A: Policy and Practice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/search?docId=0965-8564&amp;sortBy=date&amp;show=25</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0965-8564</t>
+  </si>
+  <si>
+    <t>Engineering Management</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1687,7 +1699,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1716,6 +1728,11 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2068,13 +2085,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J138"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J139"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="83" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2106,7 +2125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2117,19 +2136,19 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2140,19 +2159,19 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I3" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2163,19 +2182,19 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I4" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2186,19 +2205,19 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I5" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2209,19 +2228,19 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I6" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2232,19 +2251,19 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I7" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2255,19 +2274,19 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I8" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2278,19 +2297,19 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I9" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2301,19 +2320,19 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I10" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2324,19 +2343,19 @@
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I11" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2347,19 +2366,19 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I12" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -2370,19 +2389,19 @@
         <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I13" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -2393,19 +2412,19 @@
         <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I14" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -2416,19 +2435,19 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I15" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -2439,19 +2458,19 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I16" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -2462,19 +2481,19 @@
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I17" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2485,19 +2504,19 @@
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I18" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2508,19 +2527,19 @@
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I19" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2531,19 +2550,19 @@
         <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I20" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2554,19 +2573,19 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I21" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2577,19 +2596,19 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I22" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2600,19 +2619,19 @@
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I23" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -2623,19 +2642,19 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I24" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -2646,19 +2665,19 @@
         <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I25" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2669,19 +2688,19 @@
         <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E26" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I26" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -2692,19 +2711,19 @@
         <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I27" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2715,19 +2734,19 @@
         <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I28" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2738,19 +2757,19 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I29" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2761,19 +2780,19 @@
         <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I30" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -2784,19 +2803,19 @@
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I31" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -2807,19 +2826,19 @@
         <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E32" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I32" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -2830,19 +2849,19 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I33" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2853,19 +2872,19 @@
         <v>49</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I34" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -2876,19 +2895,19 @@
         <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I35" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -2899,19 +2918,19 @@
         <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I36" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -2919,22 +2938,19 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>552</v>
       </c>
       <c r="D37" t="s">
-        <v>188</v>
-      </c>
-      <c r="E37" t="s">
-        <v>320</v>
+        <v>554</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>445</v>
+        <v>553</v>
       </c>
       <c r="I37" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -2942,22 +2958,22 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I38" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -2965,22 +2981,22 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>552</v>
+        <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E39" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I39" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -2988,22 +3004,22 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>551</v>
       </c>
       <c r="D40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E40" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I40" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -3011,22 +3027,22 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E41" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I41" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -3034,2221 +3050,2244 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42" t="s">
+        <v>323</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I42" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
         <v>56</v>
       </c>
-      <c r="D42" t="s">
-        <v>549</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="I42" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>57</v>
-      </c>
       <c r="D43" t="s">
-        <v>193</v>
-      </c>
-      <c r="E43" t="s">
-        <v>325</v>
+        <v>548</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I43" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
         <v>11</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I44" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
         <v>11</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E45" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I45" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
         <v>11</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E46" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I46" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
         <v>11</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E47" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I47" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
         <v>11</v>
       </c>
       <c r="B48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E48" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I48" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
         <v>11</v>
       </c>
       <c r="B49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E49" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I49" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
         <v>11</v>
       </c>
       <c r="B50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E50" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I50" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
         <v>11</v>
       </c>
       <c r="B51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E51" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I51" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
         <v>11</v>
       </c>
       <c r="B52">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E52" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I52" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
         <v>11</v>
       </c>
       <c r="B53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D53" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E53" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I53" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
         <v>11</v>
       </c>
       <c r="B54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E54" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I54" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
         <v>11</v>
       </c>
       <c r="B55">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E55" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I55" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
         <v>11</v>
       </c>
       <c r="B56">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E56" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I56" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
         <v>11</v>
       </c>
       <c r="B57">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D57" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E57" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I57" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
         <v>11</v>
       </c>
       <c r="B58">
+        <v>15</v>
+      </c>
+      <c r="C58" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" t="s">
+        <v>206</v>
+      </c>
+      <c r="E58" t="s">
+        <v>338</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I58" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59">
         <v>16</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>72</v>
       </c>
-      <c r="D58" t="s">
-        <v>208</v>
-      </c>
-      <c r="E58" t="s">
-        <v>340</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="I58" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>12</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>73</v>
-      </c>
       <c r="D59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E59" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I59" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
         <v>12</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D60" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E60" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I60" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
         <v>12</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D61" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E61" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I61" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
         <v>12</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E62" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I62" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
         <v>12</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D63" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E63" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I63" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
         <v>12</v>
       </c>
       <c r="B64">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D64" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E64" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I64" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
         <v>12</v>
       </c>
       <c r="B65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D65" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E65" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I65" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
         <v>12</v>
       </c>
       <c r="B66">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D66" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E66" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I66" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
         <v>12</v>
       </c>
       <c r="B67">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E67" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I67" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
         <v>12</v>
       </c>
       <c r="B68">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D68" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E68" t="s">
-        <v>218</v>
+        <v>348</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I68" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
         <v>12</v>
       </c>
       <c r="B69">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D69" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E69" t="s">
-        <v>350</v>
+        <v>217</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I69" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
         <v>12</v>
       </c>
       <c r="B70">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E70" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I70" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
         <v>12</v>
       </c>
       <c r="B71">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D71" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E71" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I71" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
         <v>12</v>
       </c>
       <c r="B72">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D72" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E72" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I72" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
         <v>12</v>
       </c>
       <c r="B73">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C73" t="s">
-        <v>87</v>
+        <v>555</v>
       </c>
       <c r="D73" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E73" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="I73" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
         <v>12</v>
       </c>
       <c r="B74">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C74" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D74" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E74" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I74" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
         <v>12</v>
       </c>
       <c r="B75">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C75" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D75" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E75" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I75" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
         <v>12</v>
       </c>
       <c r="B76">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D76" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E76" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I76" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
         <v>12</v>
       </c>
       <c r="B77">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D77" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E77" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I77" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
         <v>12</v>
       </c>
       <c r="B78">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D78" t="s">
-        <v>551</v>
+        <v>226</v>
       </c>
       <c r="E78" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I78" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
         <v>12</v>
       </c>
       <c r="B79">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D79" t="s">
-        <v>229</v>
+        <v>550</v>
       </c>
       <c r="E79" t="s">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I79" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
         <v>12</v>
       </c>
       <c r="B80">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D80" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E80" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I80" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
         <v>12</v>
       </c>
       <c r="B81">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D81" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E81" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I81" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
         <v>12</v>
       </c>
       <c r="B82">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D82" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E82" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I82" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
         <v>12</v>
       </c>
       <c r="B83">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D83" t="s">
-        <v>363</v>
+        <v>231</v>
       </c>
       <c r="E83" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I83" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
         <v>12</v>
       </c>
       <c r="B84">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D84" t="s">
-        <v>233</v>
+        <v>362</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>362</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I84" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
         <v>12</v>
       </c>
       <c r="B85">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D85" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E85" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I85" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
         <v>12</v>
       </c>
       <c r="B86">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D86" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E86" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I86" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
         <v>12</v>
       </c>
       <c r="B87">
+        <v>30</v>
+      </c>
+      <c r="C87" t="s">
+        <v>99</v>
+      </c>
+      <c r="D87" t="s">
+        <v>234</v>
+      </c>
+      <c r="E87" t="s">
+        <v>234</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I87" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88">
         <v>31</v>
       </c>
-      <c r="C87" t="s">
-        <v>101</v>
-      </c>
-      <c r="D87" t="s">
-        <v>236</v>
-      </c>
-      <c r="E87" t="s">
-        <v>364</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="I87" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>13</v>
-      </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
       <c r="C88" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D88" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E88" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I88" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
         <v>13</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D89" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E89" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I89" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
         <v>13</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D90" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E90" t="s">
-        <v>239</v>
+        <v>365</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I90" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
         <v>13</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D91" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E91" t="s">
-        <v>367</v>
+        <v>238</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I91" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
         <v>13</v>
       </c>
       <c r="B92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E92" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I92" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
         <v>13</v>
       </c>
       <c r="B93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E93" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I93" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
         <v>13</v>
       </c>
       <c r="B94">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D94" t="s">
-        <v>548</v>
+        <v>241</v>
       </c>
       <c r="E94" t="s">
-        <v>243</v>
+        <v>368</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I94" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
         <v>13</v>
       </c>
       <c r="B95">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D95" t="s">
-        <v>244</v>
+        <v>547</v>
       </c>
       <c r="E95" t="s">
-        <v>370</v>
+        <v>242</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I95" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
         <v>13</v>
       </c>
       <c r="B96">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D96" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E96" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I96" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
         <v>13</v>
       </c>
       <c r="B97">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D97" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E97" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I97" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
         <v>13</v>
       </c>
       <c r="B98">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D98" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E98" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I98" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
         <v>13</v>
       </c>
       <c r="B99">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E99" t="s">
-        <v>248</v>
+        <v>372</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="I99" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
         <v>13</v>
       </c>
       <c r="B100">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D100" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E100" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="I100" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
         <v>13</v>
       </c>
       <c r="B101">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
+        <v>113</v>
+      </c>
+      <c r="D101" t="s">
+        <v>248</v>
+      </c>
+      <c r="E101" t="s">
+        <v>248</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I101" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102">
         <v>15</v>
       </c>
-      <c r="C101" t="s">
-        <v>115</v>
-      </c>
-      <c r="D101" t="s">
-        <v>250</v>
-      </c>
-      <c r="E101" t="s">
-        <v>250</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="I101" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>14</v>
-      </c>
-      <c r="B102">
-        <v>1</v>
-      </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E102" t="s">
-        <v>374</v>
+        <v>249</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I102" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
         <v>14</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D103" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E103" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="I103" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
         <v>14</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C104" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D104" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E104" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I104" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
         <v>14</v>
       </c>
       <c r="B105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D105" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E105" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="I105" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
         <v>14</v>
       </c>
       <c r="B106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D106" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E106" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="I106" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
         <v>14</v>
       </c>
       <c r="B107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E107" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I107" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
         <v>14</v>
       </c>
       <c r="B108">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D108" t="s">
-        <v>550</v>
+        <v>255</v>
+      </c>
+      <c r="E108" t="s">
+        <v>378</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I108" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
         <v>14</v>
       </c>
       <c r="B109">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D109" t="s">
-        <v>257</v>
-      </c>
-      <c r="E109" t="s">
-        <v>380</v>
+        <v>549</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I109" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
         <v>14</v>
       </c>
       <c r="B110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D110" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E110" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I110" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
         <v>14</v>
       </c>
       <c r="B111">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D111" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E111" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="I111" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
         <v>14</v>
       </c>
       <c r="B112">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C112" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D112" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E112" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I112" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
         <v>14</v>
       </c>
       <c r="B113">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D113" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E113" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I113" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
         <v>14</v>
       </c>
       <c r="B114">
+        <v>13</v>
+      </c>
+      <c r="C114" t="s">
+        <v>126</v>
+      </c>
+      <c r="D114" t="s">
+        <v>260</v>
+      </c>
+      <c r="E114" t="s">
+        <v>383</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="I114" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115">
         <v>15</v>
       </c>
-      <c r="C114" t="s">
-        <v>128</v>
-      </c>
-      <c r="D114" t="s">
-        <v>262</v>
-      </c>
-      <c r="E114" t="s">
-        <v>385</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="I114" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115">
-        <v>1</v>
-      </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D115" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E115" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="I115" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
         <v>15</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D116" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E116" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I116" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
         <v>15</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D117" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E117" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I117" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
         <v>15</v>
       </c>
       <c r="B118">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D118" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E118" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I118" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
         <v>15</v>
       </c>
       <c r="B119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D119" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E119" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="I119" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
         <v>15</v>
       </c>
       <c r="B120">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D120" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E120" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I120" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
         <v>15</v>
       </c>
       <c r="B121">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>133</v>
+      </c>
+      <c r="D121" t="s">
+        <v>267</v>
+      </c>
+      <c r="E121" t="s">
+        <v>390</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="I121" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122">
         <v>7</v>
       </c>
-      <c r="C121" t="s">
-        <v>135</v>
-      </c>
-      <c r="D121" t="s">
-        <v>269</v>
-      </c>
-      <c r="E121" t="s">
-        <v>392</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="I121" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>16</v>
-      </c>
-      <c r="B122">
-        <v>1</v>
-      </c>
       <c r="C122" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D122" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E122" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="I122" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
         <v>16</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D123" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E123" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="I123" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
         <v>16</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C124" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D124" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E124" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I124" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
         <v>16</v>
       </c>
       <c r="B125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D125" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E125" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="I125" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
         <v>16</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D126" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E126" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I126" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
         <v>16</v>
       </c>
       <c r="B127">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E127" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="I127" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
         <v>16</v>
       </c>
       <c r="B128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C128" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E128" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="I128" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
         <v>16</v>
       </c>
       <c r="B129">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D129" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E129" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="I129" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
         <v>16</v>
       </c>
       <c r="B130">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D130" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E130" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I130" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
         <v>16</v>
       </c>
       <c r="B131">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E131" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I131" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
         <v>16</v>
       </c>
       <c r="B132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E132" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I132" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
         <v>16</v>
       </c>
       <c r="B133">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D133" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E133" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I133" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
         <v>16</v>
       </c>
       <c r="B134">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D134" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E134" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="I134" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
         <v>16</v>
       </c>
       <c r="B135">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D135" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E135" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="I135" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
         <v>16</v>
       </c>
       <c r="B136">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D136" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E136" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I136" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
         <v>16</v>
       </c>
       <c r="B137">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C137" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D137" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E137" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I137" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
         <v>16</v>
       </c>
       <c r="B138">
+        <v>17</v>
+      </c>
+      <c r="C138" t="s">
+        <v>150</v>
+      </c>
+      <c r="D138" t="s">
+        <v>284</v>
+      </c>
+      <c r="E138" t="s">
+        <v>407</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I138" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>16</v>
+      </c>
+      <c r="B139">
         <v>18</v>
       </c>
-      <c r="C138" t="s">
-        <v>152</v>
-      </c>
-      <c r="D138" t="s">
-        <v>286</v>
-      </c>
-      <c r="E138" t="s">
-        <v>409</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="I138" t="s">
-        <v>547</v>
+      <c r="C139" t="s">
+        <v>151</v>
+      </c>
+      <c r="D139" t="s">
+        <v>285</v>
+      </c>
+      <c r="E139" t="s">
+        <v>408</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="I139" t="s">
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -5289,110 +5328,111 @@
     <hyperlink ref="F34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
     <hyperlink ref="F35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
     <hyperlink ref="F36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="F38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="F40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="F41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="F42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="F45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="F47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="F49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="F51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="F55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="F56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="F60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="F61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="F63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="F64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="F65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="F69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="F71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="F73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="F75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="F80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="F89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="F90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="F91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="F92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="F93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="F94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="F95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="F96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="F97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="F98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="F99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="F100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="F101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="F102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="F103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="F104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="F105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="F106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="F107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="F108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="F109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="F110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="F111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="F112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="F113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="F114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="F115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="F116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="F117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="F118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="F119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="F120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="F121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="F122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="F123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="F124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="F125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="F126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="F127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="F128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="F130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="F131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="F132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="F133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="F135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="F136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="F137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="F138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="F38" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F40" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="F42" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F43" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="F44" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="F45" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F46" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F47" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F48" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F49" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F50" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F51" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F52" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="F53" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F54" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F55" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F56" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="F57" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F58" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F59" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="F62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="F64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F74" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F75" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F76" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F77" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F79" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F80" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F82" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F83" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="F86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="F90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="F92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F95" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F96" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="F98" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F99" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="F100" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="F101" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="F102" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F103" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="F104" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F105" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="F106" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F107" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="F108" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F109" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="F110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="F112" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F113" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="F114" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F115" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="F116" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="F117" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="F118" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="F119" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="F120" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="F121" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="F122" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="F123" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="F124" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="F125" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="F126" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="F127" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="F128" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F129" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="F130" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="F131" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="F132" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="F133" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="F134" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="F135" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="F136" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="F137" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="F138" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="F139" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="F37" r:id="rId138" xr:uid="{BE4A9F9B-8C1C-429F-B84F-4D7FD81CAD0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId138"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId139"/>
 </worksheet>
 </file>
--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my files\onedrive\cv\dm-dut.github.io\paper-monitor\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC535E6-2FB8-4DEE-A069-CA064BA3C879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2C79A3-9AEC-4539-9186-CDCDC39CF8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="599">
   <si>
     <t>Category</t>
   </si>
@@ -1692,6 +1692,176 @@
   </si>
   <si>
     <t>Engineering Management</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of Business Research</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0148-2963</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1873-7978</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Artificial Intelligence in Medicine</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0933-3657</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data &amp; Knowledge Engineering</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0169-023X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data and Information Management</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2543-9251</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of Computational Science</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1877-7503</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Operations Research Perspectives</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2214-7160</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physics Reports</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0370-1573</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Socio-Economic Planning Sciences</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0038-0121</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of Control and Decision</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2330-7706</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Automatic Control</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Automation Science and Engineering</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Cognitive and Developmental Systems</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Computational Intelligence Magazine</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Computational Intelligence Letters</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Image Processing</t>
+  </si>
+  <si>
+    <t>IEEE Transactions on Industrial Electronics</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Industrial Informatics</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Intelligent Systems</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Intelligent Transportation Systems</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Multimedia</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE Transactions on Signal Processing</t>
+  </si>
+  <si>
+    <t>1520-9210</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1524-9050</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1541-1672</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1551-3203</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0278-0046</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1057-7149</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3070-1139</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1556-603X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2379-8920</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0018-9286</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1545-5955</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1053-587X</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1732,7 +1902,7 @@
     <font>
       <sz val="9"/>
       <name val="Carlito"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1774,12 +1944,15 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2085,10 +2258,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="83" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" customWidth="1"/>
     <col min="6" max="6" width="59.33203125" customWidth="1"/>
     <col min="8" max="8" width="16.44140625" customWidth="1"/>
   </cols>
@@ -2724,24 +2898,16 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
-      <c r="A28" t="s">
-        <v>10</v>
-      </c>
       <c r="B28">
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>559</v>
       </c>
       <c r="D28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E28" t="s">
-        <v>178</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>435</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="F28" s="2"/>
       <c r="I28" t="s">
         <v>546</v>
       </c>
@@ -2754,16 +2920,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E29" t="s">
-        <v>311</v>
+        <v>178</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I29" t="s">
         <v>546</v>
@@ -2777,16 +2943,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I30" t="s">
         <v>546</v>
@@ -2800,16 +2966,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I31" t="s">
         <v>546</v>
@@ -2823,16 +2989,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I32" t="s">
         <v>546</v>
@@ -2846,16 +3012,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I33" t="s">
         <v>546</v>
@@ -2869,16 +3035,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E34" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I34" t="s">
         <v>546</v>
@@ -2892,16 +3058,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E35" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I35" t="s">
         <v>546</v>
@@ -2915,17 +3081,15 @@
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>556</v>
       </c>
       <c r="D36" t="s">
-        <v>186</v>
+        <v>557</v>
       </c>
       <c r="E36" t="s">
-        <v>318</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>443</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="F36" s="2"/>
       <c r="I36" t="s">
         <v>546</v>
       </c>
@@ -2938,13 +3102,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>552</v>
+        <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>554</v>
+        <v>185</v>
+      </c>
+      <c r="E37" t="s">
+        <v>317</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>553</v>
+        <v>442</v>
       </c>
       <c r="I37" t="s">
         <v>546</v>
@@ -2958,16 +3125,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I38" t="s">
         <v>546</v>
@@ -2981,16 +3148,13 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>552</v>
       </c>
       <c r="D39" t="s">
-        <v>188</v>
-      </c>
-      <c r="E39" t="s">
-        <v>320</v>
+        <v>554</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>445</v>
+        <v>553</v>
       </c>
       <c r="I39" t="s">
         <v>546</v>
@@ -3004,16 +3168,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>551</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I40" t="s">
         <v>546</v>
@@ -3027,16 +3191,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E41" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I41" t="s">
         <v>546</v>
@@ -3050,16 +3214,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>551</v>
       </c>
       <c r="D42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E42" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I42" t="s">
         <v>546</v>
@@ -3073,13 +3237,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>548</v>
+        <v>190</v>
+      </c>
+      <c r="E43" t="s">
+        <v>322</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I43" t="s">
         <v>546</v>
@@ -3087,22 +3254,22 @@
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I44" t="s">
         <v>546</v>
@@ -3110,137 +3277,106 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>571</v>
       </c>
       <c r="D45" t="s">
-        <v>193</v>
-      </c>
-      <c r="E45" t="s">
-        <v>325</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>451</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="F45" s="2"/>
       <c r="I45" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>567</v>
       </c>
       <c r="D46" t="s">
-        <v>194</v>
-      </c>
-      <c r="E46" t="s">
-        <v>326</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>452</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="F46" s="2"/>
       <c r="I46" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>563</v>
       </c>
       <c r="D47" t="s">
-        <v>195</v>
-      </c>
-      <c r="E47" t="s">
-        <v>327</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>453</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="F47" s="2"/>
       <c r="I47" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>561</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
-      </c>
-      <c r="E48" t="s">
-        <v>328</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>454</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="F48" s="2"/>
       <c r="I48" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>569</v>
       </c>
       <c r="D49" t="s">
-        <v>197</v>
-      </c>
-      <c r="E49" t="s">
-        <v>329</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>455</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="F49" s="2"/>
       <c r="I49" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B50">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>565</v>
       </c>
       <c r="D50" t="s">
-        <v>198</v>
-      </c>
-      <c r="E50" t="s">
-        <v>330</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>456</v>
+        <v>566</v>
       </c>
       <c r="I50" t="s">
         <v>546</v>
@@ -3248,22 +3384,19 @@
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s">
-        <v>199</v>
-      </c>
-      <c r="E51" t="s">
-        <v>331</v>
+        <v>548</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="I51" t="s">
         <v>546</v>
@@ -3274,19 +3407,19 @@
         <v>11</v>
       </c>
       <c r="B52">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E52" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="I52" t="s">
         <v>546</v>
@@ -3297,19 +3430,19 @@
         <v>11</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E53" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="I53" t="s">
         <v>546</v>
@@ -3320,19 +3453,19 @@
         <v>11</v>
       </c>
       <c r="B54">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D54" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E54" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="I54" t="s">
         <v>546</v>
@@ -3343,19 +3476,19 @@
         <v>11</v>
       </c>
       <c r="B55">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E55" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I55" t="s">
         <v>546</v>
@@ -3366,19 +3499,19 @@
         <v>11</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E56" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="I56" t="s">
         <v>546</v>
@@ -3389,19 +3522,19 @@
         <v>11</v>
       </c>
       <c r="B57">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E57" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="I57" t="s">
         <v>546</v>
@@ -3412,19 +3545,19 @@
         <v>11</v>
       </c>
       <c r="B58">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D58" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E58" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="I58" t="s">
         <v>546</v>
@@ -3435,19 +3568,19 @@
         <v>11</v>
       </c>
       <c r="B59">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E59" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="I59" t="s">
         <v>546</v>
@@ -3455,22 +3588,22 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D60" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E60" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I60" t="s">
         <v>546</v>
@@ -3478,22 +3611,22 @@
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D61" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E61" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="I61" t="s">
         <v>546</v>
@@ -3501,22 +3634,22 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D62" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E62" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I62" t="s">
         <v>546</v>
@@ -3524,22 +3657,22 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63">
         <v>12</v>
       </c>
-      <c r="B63">
-        <v>4</v>
-      </c>
       <c r="C63" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E63" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="I63" t="s">
         <v>546</v>
@@ -3547,22 +3680,22 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E64" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="I64" t="s">
         <v>546</v>
@@ -3570,22 +3703,22 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E65" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="I65" t="s">
         <v>546</v>
@@ -3593,22 +3726,22 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D66" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E66" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="I66" t="s">
         <v>546</v>
@@ -3616,22 +3749,22 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D67" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E67" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="I67" t="s">
         <v>546</v>
@@ -3642,19 +3775,19 @@
         <v>12</v>
       </c>
       <c r="B68">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E68" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="I68" t="s">
         <v>546</v>
@@ -3665,19 +3798,19 @@
         <v>12</v>
       </c>
       <c r="B69">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D69" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E69" t="s">
-        <v>217</v>
+        <v>341</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="I69" t="s">
         <v>546</v>
@@ -3688,19 +3821,19 @@
         <v>12</v>
       </c>
       <c r="B70">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D70" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E70" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="I70" t="s">
         <v>546</v>
@@ -3711,19 +3844,19 @@
         <v>12</v>
       </c>
       <c r="B71">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D71" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="I71" t="s">
         <v>546</v>
@@ -3734,19 +3867,19 @@
         <v>12</v>
       </c>
       <c r="B72">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C72" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E72" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="I72" t="s">
         <v>546</v>
@@ -3757,19 +3890,19 @@
         <v>12</v>
       </c>
       <c r="B73">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E73" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="I73" t="s">
         <v>546</v>
@@ -3780,19 +3913,19 @@
         <v>12</v>
       </c>
       <c r="B74">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D74" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E74" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="I74" t="s">
         <v>546</v>
@@ -3803,19 +3936,19 @@
         <v>12</v>
       </c>
       <c r="B75">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E75" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="I75" t="s">
         <v>546</v>
@@ -3826,19 +3959,19 @@
         <v>12</v>
       </c>
       <c r="B76">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E76" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="I76" t="s">
         <v>546</v>
@@ -3849,19 +3982,19 @@
         <v>12</v>
       </c>
       <c r="B77">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E77" t="s">
-        <v>356</v>
+        <v>217</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="I77" t="s">
         <v>546</v>
@@ -3872,19 +4005,19 @@
         <v>12</v>
       </c>
       <c r="B78">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E78" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="I78" t="s">
         <v>546</v>
@@ -3895,19 +4028,19 @@
         <v>12</v>
       </c>
       <c r="B79">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>550</v>
+        <v>219</v>
       </c>
       <c r="E79" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="I79" t="s">
         <v>546</v>
@@ -3918,19 +4051,19 @@
         <v>12</v>
       </c>
       <c r="B80">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E80" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="I80" t="s">
         <v>546</v>
@@ -3941,19 +4074,19 @@
         <v>12</v>
       </c>
       <c r="B81">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C81" t="s">
-        <v>93</v>
+        <v>555</v>
       </c>
       <c r="D81" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E81" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="I81" t="s">
         <v>546</v>
@@ -3964,19 +4097,19 @@
         <v>12</v>
       </c>
       <c r="B82">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D82" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E82" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="I82" t="s">
         <v>546</v>
@@ -3987,19 +4120,19 @@
         <v>12</v>
       </c>
       <c r="B83">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D83" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E83" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="I83" t="s">
         <v>546</v>
@@ -4010,19 +4143,19 @@
         <v>12</v>
       </c>
       <c r="B84">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D84" t="s">
-        <v>362</v>
+        <v>224</v>
       </c>
       <c r="E84" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="I84" t="s">
         <v>546</v>
@@ -4033,19 +4166,19 @@
         <v>12</v>
       </c>
       <c r="B85">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D85" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E85" t="s">
-        <v>232</v>
+        <v>356</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="I85" t="s">
         <v>546</v>
@@ -4056,19 +4189,19 @@
         <v>12</v>
       </c>
       <c r="B86">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D86" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E86" t="s">
-        <v>233</v>
+        <v>357</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="I86" t="s">
         <v>546</v>
@@ -4079,19 +4212,19 @@
         <v>12</v>
       </c>
       <c r="B87">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D87" t="s">
-        <v>234</v>
+        <v>550</v>
       </c>
       <c r="E87" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="I87" t="s">
         <v>546</v>
@@ -4102,19 +4235,19 @@
         <v>12</v>
       </c>
       <c r="B88">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D88" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E88" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="I88" t="s">
         <v>546</v>
@@ -4122,22 +4255,22 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D89" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E89" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="I89" t="s">
         <v>546</v>
@@ -4145,22 +4278,22 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C90" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D90" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E90" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="I90" t="s">
         <v>546</v>
@@ -4168,22 +4301,22 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D91" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E91" t="s">
-        <v>238</v>
+        <v>361</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="I91" t="s">
         <v>546</v>
@@ -4191,22 +4324,22 @@
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D92" t="s">
-        <v>239</v>
+        <v>362</v>
       </c>
       <c r="E92" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="I92" t="s">
         <v>546</v>
@@ -4214,22 +4347,22 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D93" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E93" t="s">
-        <v>367</v>
+        <v>232</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I93" t="s">
         <v>546</v>
@@ -4237,22 +4370,22 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B94">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D94" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E94" t="s">
-        <v>368</v>
+        <v>233</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="I94" t="s">
         <v>546</v>
@@ -4260,22 +4393,22 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B95">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D95" t="s">
-        <v>547</v>
+        <v>234</v>
       </c>
       <c r="E95" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="I95" t="s">
         <v>546</v>
@@ -4283,22 +4416,22 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B96">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C96" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D96" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E96" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="I96" t="s">
         <v>546</v>
@@ -4309,19 +4442,19 @@
         <v>13</v>
       </c>
       <c r="B97">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D97" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="I97" t="s">
         <v>546</v>
@@ -4332,19 +4465,19 @@
         <v>13</v>
       </c>
       <c r="B98">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C98" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D98" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E98" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="I98" t="s">
         <v>546</v>
@@ -4355,19 +4488,19 @@
         <v>13</v>
       </c>
       <c r="B99">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D99" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E99" t="s">
-        <v>372</v>
+        <v>238</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="I99" t="s">
         <v>546</v>
@@ -4378,19 +4511,19 @@
         <v>13</v>
       </c>
       <c r="B100">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E100" t="s">
-        <v>247</v>
+        <v>366</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="I100" t="s">
         <v>546</v>
@@ -4401,19 +4534,19 @@
         <v>13</v>
       </c>
       <c r="B101">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C101" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D101" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E101" t="s">
-        <v>248</v>
+        <v>367</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="I101" t="s">
         <v>546</v>
@@ -4424,19 +4557,19 @@
         <v>13</v>
       </c>
       <c r="B102">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D102" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E102" t="s">
-        <v>249</v>
+        <v>368</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="I102" t="s">
         <v>546</v>
@@ -4444,22 +4577,22 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D103" t="s">
-        <v>250</v>
+        <v>547</v>
       </c>
       <c r="E103" t="s">
-        <v>373</v>
+        <v>242</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="I103" t="s">
         <v>546</v>
@@ -4467,22 +4600,22 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D104" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E104" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="I104" t="s">
         <v>546</v>
@@ -4490,22 +4623,22 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D105" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E105" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="I105" t="s">
         <v>546</v>
@@ -4513,22 +4646,22 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B106">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D106" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E106" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="I106" t="s">
         <v>546</v>
@@ -4536,22 +4669,22 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B107">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E107" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="I107" t="s">
         <v>546</v>
@@ -4559,65 +4692,58 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B108">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="D108" t="s">
-        <v>255</v>
-      </c>
-      <c r="E108" t="s">
-        <v>378</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>514</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="F108" s="2"/>
       <c r="I108" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B109">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>121</v>
+        <v>585</v>
       </c>
       <c r="D109" t="s">
-        <v>549</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="F109" s="2"/>
       <c r="I109" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110">
         <v>14</v>
       </c>
-      <c r="B110">
-        <v>8</v>
-      </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E110" t="s">
-        <v>379</v>
+        <v>247</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="I110" t="s">
         <v>546</v>
@@ -4625,22 +4751,22 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B111">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D111" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="E111" t="s">
-        <v>380</v>
+        <v>248</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="I111" t="s">
         <v>546</v>
@@ -4648,22 +4774,22 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B112">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E112" t="s">
-        <v>381</v>
+        <v>249</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="I112" t="s">
         <v>546</v>
@@ -4671,252 +4797,202 @@
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B113">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>125</v>
+        <v>586</v>
       </c>
       <c r="D113" t="s">
-        <v>259</v>
-      </c>
-      <c r="E113" t="s">
-        <v>382</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>519</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="F113" s="2"/>
       <c r="I113" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B114">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>126</v>
+        <v>584</v>
       </c>
       <c r="D114" t="s">
-        <v>260</v>
-      </c>
-      <c r="E114" t="s">
-        <v>383</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>520</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="F114" s="2"/>
       <c r="I114" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B115">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C115" t="s">
-        <v>127</v>
+        <v>581</v>
       </c>
       <c r="D115" t="s">
-        <v>261</v>
-      </c>
-      <c r="E115" t="s">
-        <v>384</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>521</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="F115" s="2"/>
       <c r="I115" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C116" t="s">
-        <v>128</v>
+        <v>582</v>
       </c>
       <c r="D116" t="s">
-        <v>262</v>
-      </c>
-      <c r="E116" t="s">
-        <v>385</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>522</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="F116" s="2"/>
       <c r="I116" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
-        <v>129</v>
+        <v>575</v>
       </c>
       <c r="D117" t="s">
-        <v>263</v>
-      </c>
-      <c r="E117" t="s">
-        <v>386</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>523</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="F117" s="2"/>
       <c r="I117" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C118" t="s">
-        <v>130</v>
+        <v>576</v>
       </c>
       <c r="D118" t="s">
-        <v>264</v>
-      </c>
-      <c r="E118" t="s">
-        <v>387</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>524</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="F118" s="2"/>
       <c r="I118" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C119" t="s">
-        <v>131</v>
-      </c>
-      <c r="D119" t="s">
-        <v>265</v>
-      </c>
-      <c r="E119" t="s">
-        <v>388</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>525</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="F119" s="2"/>
       <c r="I119" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C120" t="s">
-        <v>132</v>
+        <v>578</v>
       </c>
       <c r="D120" t="s">
-        <v>266</v>
-      </c>
-      <c r="E120" t="s">
-        <v>389</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>526</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="F120" s="2"/>
       <c r="I120" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B121">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C121" t="s">
-        <v>133</v>
+        <v>579</v>
       </c>
       <c r="D121" t="s">
-        <v>267</v>
-      </c>
-      <c r="E121" t="s">
-        <v>390</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>527</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="F121" s="2"/>
       <c r="I121" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B122">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>134</v>
+        <v>583</v>
       </c>
       <c r="D122" t="s">
-        <v>268</v>
-      </c>
-      <c r="E122" t="s">
-        <v>391</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>528</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="F122" s="2"/>
       <c r="I122" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D123" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E123" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="I123" t="s">
         <v>546</v>
@@ -4924,22 +5000,22 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B124">
         <v>2</v>
       </c>
       <c r="C124" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D124" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="E124" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="I124" t="s">
         <v>546</v>
@@ -4947,22 +5023,22 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B125">
         <v>3</v>
       </c>
       <c r="C125" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D125" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="E125" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="I125" t="s">
         <v>546</v>
@@ -4970,22 +5046,22 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B126">
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D126" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="E126" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="I126" t="s">
         <v>546</v>
@@ -4993,22 +5069,22 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B127">
         <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="D127" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="E127" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="I127" t="s">
         <v>546</v>
@@ -5016,22 +5092,22 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B128">
         <v>6</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D128" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="E128" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="I128" t="s">
         <v>546</v>
@@ -5039,22 +5115,19 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B129">
         <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="D129" t="s">
-        <v>275</v>
-      </c>
-      <c r="E129" t="s">
-        <v>398</v>
+        <v>549</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="I129" t="s">
         <v>546</v>
@@ -5062,22 +5135,22 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B130">
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D130" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="E130" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="I130" t="s">
         <v>546</v>
@@ -5085,22 +5158,22 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B131">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C131" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="D131" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="E131" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="I131" t="s">
         <v>546</v>
@@ -5108,22 +5181,22 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B132">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D132" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="E132" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="I132" t="s">
         <v>546</v>
@@ -5131,22 +5204,22 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B133">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D133" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="E133" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="I133" t="s">
         <v>546</v>
@@ -5154,22 +5227,22 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B134">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D134" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E134" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="I134" t="s">
         <v>546</v>
@@ -5177,22 +5250,22 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B135">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="D135" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="E135" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="I135" t="s">
         <v>546</v>
@@ -5200,22 +5273,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B136">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C136" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D136" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E136" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="I136" t="s">
         <v>546</v>
@@ -5223,22 +5296,22 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B137">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C137" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="D137" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="E137" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="I137" t="s">
         <v>546</v>
@@ -5246,22 +5319,22 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B138">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C138" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D138" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="E138" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="I138" t="s">
         <v>546</v>
@@ -5269,24 +5342,499 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>131</v>
+      </c>
+      <c r="D139" t="s">
+        <v>265</v>
+      </c>
+      <c r="E139" t="s">
+        <v>388</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="I139" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+      <c r="C140" t="s">
+        <v>132</v>
+      </c>
+      <c r="D140" t="s">
+        <v>266</v>
+      </c>
+      <c r="E140" t="s">
+        <v>389</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="I140" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>133</v>
+      </c>
+      <c r="D141" t="s">
+        <v>267</v>
+      </c>
+      <c r="E141" t="s">
+        <v>390</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="I141" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142">
+        <v>7</v>
+      </c>
+      <c r="C142" t="s">
+        <v>134</v>
+      </c>
+      <c r="D142" t="s">
+        <v>268</v>
+      </c>
+      <c r="E142" t="s">
+        <v>391</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="I142" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
         <v>16</v>
       </c>
-      <c r="B139">
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>135</v>
+      </c>
+      <c r="D143" t="s">
+        <v>269</v>
+      </c>
+      <c r="E143" t="s">
+        <v>392</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="I143" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>16</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>136</v>
+      </c>
+      <c r="D144" t="s">
+        <v>270</v>
+      </c>
+      <c r="E144" t="s">
+        <v>393</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="I144" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>16</v>
+      </c>
+      <c r="B145">
+        <v>3</v>
+      </c>
+      <c r="C145" t="s">
+        <v>137</v>
+      </c>
+      <c r="D145" t="s">
+        <v>271</v>
+      </c>
+      <c r="E145" t="s">
+        <v>394</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="I145" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>16</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146" t="s">
+        <v>138</v>
+      </c>
+      <c r="D146" t="s">
+        <v>272</v>
+      </c>
+      <c r="E146" t="s">
+        <v>395</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="I146" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>16</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+      <c r="C147" t="s">
+        <v>139</v>
+      </c>
+      <c r="D147" t="s">
+        <v>273</v>
+      </c>
+      <c r="E147" t="s">
+        <v>396</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="I147" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>16</v>
+      </c>
+      <c r="B148">
+        <v>6</v>
+      </c>
+      <c r="C148" t="s">
+        <v>140</v>
+      </c>
+      <c r="D148" t="s">
+        <v>274</v>
+      </c>
+      <c r="E148" t="s">
+        <v>397</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="I148" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>16</v>
+      </c>
+      <c r="B149">
+        <v>7</v>
+      </c>
+      <c r="C149" t="s">
+        <v>141</v>
+      </c>
+      <c r="D149" t="s">
+        <v>275</v>
+      </c>
+      <c r="E149" t="s">
+        <v>398</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I149" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>16</v>
+      </c>
+      <c r="B150">
+        <v>8</v>
+      </c>
+      <c r="C150" t="s">
+        <v>142</v>
+      </c>
+      <c r="D150" t="s">
+        <v>276</v>
+      </c>
+      <c r="E150" t="s">
+        <v>399</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="I150" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>16</v>
+      </c>
+      <c r="B151">
+        <v>9</v>
+      </c>
+      <c r="C151" t="s">
+        <v>143</v>
+      </c>
+      <c r="D151" t="s">
+        <v>277</v>
+      </c>
+      <c r="E151" t="s">
+        <v>400</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="I151" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>16</v>
+      </c>
+      <c r="B152">
+        <v>10</v>
+      </c>
+      <c r="C152" t="s">
+        <v>144</v>
+      </c>
+      <c r="D152" t="s">
+        <v>278</v>
+      </c>
+      <c r="E152" t="s">
+        <v>401</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="I152" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>16</v>
+      </c>
+      <c r="B153">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>145</v>
+      </c>
+      <c r="D153" t="s">
+        <v>279</v>
+      </c>
+      <c r="E153" t="s">
+        <v>402</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="I153" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>16</v>
+      </c>
+      <c r="B154">
+        <v>12</v>
+      </c>
+      <c r="C154" t="s">
+        <v>146</v>
+      </c>
+      <c r="D154" t="s">
+        <v>280</v>
+      </c>
+      <c r="E154" t="s">
+        <v>403</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I154" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>16</v>
+      </c>
+      <c r="B155">
+        <v>13</v>
+      </c>
+      <c r="C155" t="s">
+        <v>147</v>
+      </c>
+      <c r="D155" t="s">
+        <v>281</v>
+      </c>
+      <c r="E155" t="s">
+        <v>404</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="I155" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>16</v>
+      </c>
+      <c r="B156">
+        <v>14</v>
+      </c>
+      <c r="C156" t="s">
+        <v>573</v>
+      </c>
+      <c r="D156" t="s">
+        <v>574</v>
+      </c>
+      <c r="F156" s="2"/>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>16</v>
+      </c>
+      <c r="B157">
+        <v>15</v>
+      </c>
+      <c r="C157" t="s">
+        <v>148</v>
+      </c>
+      <c r="D157" t="s">
+        <v>282</v>
+      </c>
+      <c r="E157" t="s">
+        <v>405</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="I157" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>16</v>
+      </c>
+      <c r="B158">
+        <v>16</v>
+      </c>
+      <c r="C158" t="s">
+        <v>149</v>
+      </c>
+      <c r="D158" t="s">
+        <v>283</v>
+      </c>
+      <c r="E158" t="s">
+        <v>406</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I158" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>16</v>
+      </c>
+      <c r="B159">
+        <v>17</v>
+      </c>
+      <c r="C159" t="s">
+        <v>150</v>
+      </c>
+      <c r="D159" t="s">
+        <v>284</v>
+      </c>
+      <c r="E159" t="s">
+        <v>407</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I159" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>16</v>
+      </c>
+      <c r="B160">
         <v>18</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C160" t="s">
         <v>151</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D160" t="s">
         <v>285</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E160" t="s">
         <v>408</v>
       </c>
-      <c r="F139" s="2" t="s">
+      <c r="F160" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="I139" t="s">
+      <c r="I160" t="s">
         <v>546</v>
       </c>
     </row>
@@ -5319,118 +5867,118 @@
     <hyperlink ref="F25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="F26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
     <hyperlink ref="F27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="F28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="F30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="F36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F38" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="F39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F40" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="F41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="F42" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="F43" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F44" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F45" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="F46" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F47" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="F48" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F49" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="F50" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F51" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="F52" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F53" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F54" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F55" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="F56" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="F57" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F58" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F59" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="F61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="F62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="F64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="F65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="F66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="F70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="F72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="F74" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F75" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="F76" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F77" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F79" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F80" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="F81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F82" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F83" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="F90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="F91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="F92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="F93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="F94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="F95" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="F96" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="F97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="F98" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="F99" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="F100" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="F101" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="F102" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="F103" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="F104" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="F105" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="F106" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="F107" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="F108" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="F109" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="F110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="F111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="F112" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="F113" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="F114" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="F115" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="F116" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="F117" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="F118" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="F119" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="F120" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="F121" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="F122" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="F123" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="F124" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="F125" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="F126" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="F127" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="F128" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="F129" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F130" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="F131" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="F132" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="F133" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="F134" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F135" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="F136" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="F137" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="F138" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="F139" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="F37" r:id="rId138" xr:uid="{BE4A9F9B-8C1C-429F-B84F-4D7FD81CAD0E}"/>
+    <hyperlink ref="F29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="F32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F33" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F34" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F37" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F38" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F40" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F41" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F42" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F43" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="F44" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F51" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="F52" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="F53" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F54" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F55" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F56" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F57" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F58" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F59" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F60" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="F61" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F62" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F63" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F64" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="F65" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F66" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F67" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F68" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F69" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="F70" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F71" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="F72" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F73" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F74" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F75" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F76" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F77" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F78" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F79" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F80" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F81" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F82" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F83" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F84" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F85" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F86" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F87" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F88" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F89" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F90" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F91" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F92" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F93" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="F94" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F95" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F96" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F97" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="F98" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F99" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="F100" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F101" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F102" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F103" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F104" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F105" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="F106" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F107" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="F110" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="F111" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="F112" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F123" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="F124" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F125" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="F126" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F127" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="F128" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F129" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="F130" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F131" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="F132" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F133" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="F134" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F135" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="F136" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="F137" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="F138" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="F139" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="F140" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="F141" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="F142" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="F143" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="F144" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="F145" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="F146" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="F147" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="F148" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F149" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="F150" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="F151" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="F152" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="F153" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="F154" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="F155" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="F157" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="F158" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="F159" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="F160" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="F39" r:id="rId138" xr:uid="{BE4A9F9B-8C1C-429F-B84F-4D7FD81CAD0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId139"/>

--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\paper-monitor\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Onedrive\CV\dm-dut.github.io\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2C79A3-9AEC-4539-9186-CDCDC39CF8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0EB9C8-C617-445B-A51D-83EB4CB191E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="615">
   <si>
     <t>Category</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>ACM</t>
-  </si>
-  <si>
-    <t>Wiley/Taylor/WorldScientific</t>
   </si>
   <si>
     <t>Applied Soft Computing</t>
@@ -1862,6 +1859,74 @@
   </si>
   <si>
     <t>1053-587X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0276-7783</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Management Information Systems Quarterly</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of the Association for Information Systems	</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">European Journal of Information Systems	</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Information Systems Journal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Information Systems Frontiers</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Information Technology and People</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internet Research</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal of the Association for Information Science and Technology</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wiley/Taylor/WorldSci/Emerald</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1536-9323</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0960-085X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0959-3845</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1066-2243</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1350-1917</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2330-1635</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1387-3326</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2258,13 +2323,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J160"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:J168"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
+    <col min="1" max="1" width="25.08984375" customWidth="1"/>
     <col min="3" max="3" width="83" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" customWidth="1"/>
-    <col min="6" max="6" width="59.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" customWidth="1"/>
+    <col min="6" max="6" width="59.36328125" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2307,19 +2373,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
@@ -2330,19 +2396,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
@@ -2353,19 +2419,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
@@ -2376,19 +2442,19 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15">
@@ -2399,19 +2465,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
@@ -2422,19 +2488,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
@@ -2445,19 +2511,19 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15">
@@ -2468,19 +2534,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
@@ -2491,19 +2557,19 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15">
@@ -2514,19 +2580,19 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15">
@@ -2537,19 +2603,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15">
@@ -2560,19 +2626,19 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15">
@@ -2583,19 +2649,19 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I14" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15">
@@ -2606,19 +2672,19 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15">
@@ -2629,19 +2695,19 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I16" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -2652,19 +2718,19 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -2675,19 +2741,19 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I18" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -2698,19 +2764,19 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I19" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -2721,19 +2787,19 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I20" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -2744,19 +2810,19 @@
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I21" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -2767,19 +2833,19 @@
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I22" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -2790,19 +2856,19 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I23" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -2813,19 +2879,19 @@
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I24" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -2836,19 +2902,19 @@
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I25" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -2859,19 +2925,19 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I26" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -2882,19 +2948,19 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E27" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I27" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -2902,14 +2968,14 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
+        <v>558</v>
+      </c>
+      <c r="D28" t="s">
         <v>559</v>
-      </c>
-      <c r="D28" t="s">
-        <v>560</v>
       </c>
       <c r="F28" s="2"/>
       <c r="I28" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -2920,19 +2986,19 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I29" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -2943,19 +3009,19 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I30" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -2966,19 +3032,19 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E31" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I31" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -2989,19 +3055,19 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -3012,19 +3078,19 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E33" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I33" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -3035,19 +3101,19 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E34" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I34" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -3058,19 +3124,19 @@
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I35" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -3081,17 +3147,17 @@
         <v>35</v>
       </c>
       <c r="C36" t="s">
+        <v>555</v>
+      </c>
+      <c r="D36" t="s">
         <v>556</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>557</v>
-      </c>
-      <c r="E36" t="s">
-        <v>558</v>
       </c>
       <c r="F36" s="2"/>
       <c r="I36" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -3102,19 +3168,19 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I37" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -3125,19 +3191,19 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I38" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -3148,16 +3214,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
+        <v>551</v>
+      </c>
+      <c r="D39" t="s">
+        <v>553</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D39" t="s">
-        <v>554</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>553</v>
-      </c>
       <c r="I39" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -3168,19 +3234,19 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I40" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -3191,19 +3257,19 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I41" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -3214,19 +3280,19 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I42" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
@@ -3237,19 +3303,19 @@
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I43" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -3260,19 +3326,19 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I44" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
@@ -3283,14 +3349,14 @@
         <v>44</v>
       </c>
       <c r="C45" t="s">
+        <v>570</v>
+      </c>
+      <c r="D45" t="s">
         <v>571</v>
-      </c>
-      <c r="D45" t="s">
-        <v>572</v>
       </c>
       <c r="F45" s="2"/>
       <c r="I45" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
@@ -3301,14 +3367,14 @@
         <v>45</v>
       </c>
       <c r="C46" t="s">
+        <v>566</v>
+      </c>
+      <c r="D46" t="s">
         <v>567</v>
-      </c>
-      <c r="D46" t="s">
-        <v>568</v>
       </c>
       <c r="F46" s="2"/>
       <c r="I46" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -3319,14 +3385,14 @@
         <v>46</v>
       </c>
       <c r="C47" t="s">
+        <v>562</v>
+      </c>
+      <c r="D47" t="s">
         <v>563</v>
-      </c>
-      <c r="D47" t="s">
-        <v>564</v>
       </c>
       <c r="F47" s="2"/>
       <c r="I47" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -3337,14 +3403,14 @@
         <v>47</v>
       </c>
       <c r="C48" t="s">
+        <v>560</v>
+      </c>
+      <c r="D48" t="s">
         <v>561</v>
-      </c>
-      <c r="D48" t="s">
-        <v>562</v>
       </c>
       <c r="F48" s="2"/>
       <c r="I48" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
@@ -3355,14 +3421,14 @@
         <v>48</v>
       </c>
       <c r="C49" t="s">
+        <v>568</v>
+      </c>
+      <c r="D49" t="s">
         <v>569</v>
-      </c>
-      <c r="D49" t="s">
-        <v>570</v>
       </c>
       <c r="F49" s="2"/>
       <c r="I49" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3373,13 +3439,13 @@
         <v>49</v>
       </c>
       <c r="C50" t="s">
+        <v>564</v>
+      </c>
+      <c r="D50" t="s">
         <v>565</v>
       </c>
-      <c r="D50" t="s">
-        <v>566</v>
-      </c>
       <c r="I50" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
@@ -3390,16 +3456,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D51" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I51" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
@@ -3410,19 +3476,19 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E52" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I52" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
@@ -3433,19 +3499,19 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I53" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
@@ -3456,19 +3522,19 @@
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E54" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I54" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
@@ -3479,19 +3545,19 @@
         <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I55" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
@@ -3502,19 +3568,19 @@
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E56" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I56" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
@@ -3525,19 +3591,19 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E57" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I57" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -3548,19 +3614,19 @@
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E58" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I58" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
@@ -3571,19 +3637,19 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I59" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
@@ -3594,19 +3660,19 @@
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E60" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I60" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
@@ -3617,19 +3683,19 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D61" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E61" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I61" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
@@ -3640,19 +3706,19 @@
         <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E62" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I62" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
@@ -3663,19 +3729,19 @@
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D63" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I63" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
@@ -3686,19 +3752,19 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D64" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I64" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
@@ -3709,19 +3775,19 @@
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E65" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I65" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
@@ -3732,19 +3798,19 @@
         <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D66" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E66" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I66" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
@@ -3755,19 +3821,19 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D67" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E67" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I67" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
@@ -3778,19 +3844,19 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D68" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I68" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
@@ -3801,19 +3867,19 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E69" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I69" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
@@ -3824,19 +3890,19 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D70" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E70" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I70" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
@@ -3847,19 +3913,19 @@
         <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E71" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I71" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
@@ -3870,19 +3936,19 @@
         <v>5</v>
       </c>
       <c r="C72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D72" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E72" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I72" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
@@ -3893,19 +3959,19 @@
         <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E73" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I73" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
@@ -3916,19 +3982,19 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E74" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I74" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
@@ -3939,19 +4005,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D75" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E75" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I75" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
@@ -3962,19 +4028,19 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D76" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E76" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I76" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
@@ -3985,19 +4051,19 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I77" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
@@ -4008,19 +4074,19 @@
         <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D78" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E78" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I78" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
@@ -4031,19 +4097,19 @@
         <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D79" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E79" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I79" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
@@ -4054,19 +4120,19 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D80" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E80" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I80" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
@@ -4077,19 +4143,19 @@
         <v>14</v>
       </c>
       <c r="C81" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E81" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I81" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
@@ -4100,19 +4166,19 @@
         <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E82" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I82" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
@@ -4123,19 +4189,19 @@
         <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D83" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E83" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I83" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
@@ -4146,19 +4212,19 @@
         <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D84" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E84" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I84" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
@@ -4169,20 +4235,12 @@
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>89</v>
+        <v>603</v>
       </c>
       <c r="D85" t="s">
-        <v>225</v>
-      </c>
-      <c r="E85" t="s">
-        <v>356</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="I85" t="s">
-        <v>546</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="F85" s="2"/>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
@@ -4192,19 +4250,19 @@
         <v>19</v>
       </c>
       <c r="C86" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D86" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E86" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I86" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
@@ -4215,19 +4273,19 @@
         <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D87" t="s">
-        <v>550</v>
+        <v>225</v>
       </c>
       <c r="E87" t="s">
-        <v>227</v>
+        <v>356</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I87" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
@@ -4238,19 +4296,19 @@
         <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>228</v>
+        <v>549</v>
       </c>
       <c r="E88" t="s">
-        <v>358</v>
+        <v>226</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I88" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
@@ -4261,19 +4319,19 @@
         <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D89" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E89" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I89" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
@@ -4284,19 +4342,19 @@
         <v>23</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D90" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E90" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I90" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
@@ -4307,19 +4365,19 @@
         <v>24</v>
       </c>
       <c r="C91" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D91" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E91" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I91" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
@@ -4330,19 +4388,19 @@
         <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D92" t="s">
-        <v>362</v>
+        <v>230</v>
       </c>
       <c r="E92" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I92" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
@@ -4353,19 +4411,19 @@
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D93" t="s">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="E93" t="s">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I93" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
@@ -4376,19 +4434,19 @@
         <v>27</v>
       </c>
       <c r="C94" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D94" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E94" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I94" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
@@ -4399,19 +4457,19 @@
         <v>28</v>
       </c>
       <c r="C95" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D95" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E95" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I95" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
@@ -4422,42 +4480,42 @@
         <v>29</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D96" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E96" t="s">
-        <v>363</v>
+        <v>233</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I96" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E97" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I97" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
@@ -4465,22 +4523,22 @@
         <v>13</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D98" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E98" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I98" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
@@ -4488,22 +4546,22 @@
         <v>13</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D99" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>238</v>
+        <v>364</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I99" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
@@ -4511,22 +4569,22 @@
         <v>13</v>
       </c>
       <c r="B100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D100" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E100" t="s">
-        <v>366</v>
+        <v>237</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I100" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
@@ -4534,22 +4592,22 @@
         <v>13</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D101" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E101" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I101" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
@@ -4557,22 +4615,22 @@
         <v>13</v>
       </c>
       <c r="B102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C102" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D102" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E102" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I102" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
@@ -4580,22 +4638,22 @@
         <v>13</v>
       </c>
       <c r="B103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C103" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D103" t="s">
-        <v>547</v>
+        <v>240</v>
       </c>
       <c r="E103" t="s">
-        <v>242</v>
+        <v>367</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I103" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
@@ -4603,22 +4661,22 @@
         <v>13</v>
       </c>
       <c r="B104">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C104" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D104" t="s">
-        <v>243</v>
+        <v>546</v>
       </c>
       <c r="E104" t="s">
-        <v>369</v>
+        <v>241</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I104" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
@@ -4626,22 +4684,22 @@
         <v>13</v>
       </c>
       <c r="B105">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D105" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E105" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I105" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
@@ -4649,22 +4707,22 @@
         <v>13</v>
       </c>
       <c r="B106">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D106" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E106" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I106" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
@@ -4672,22 +4730,22 @@
         <v>13</v>
       </c>
       <c r="B107">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D107" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E107" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I107" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
@@ -4695,17 +4753,22 @@
         <v>13</v>
       </c>
       <c r="B108">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108" t="s">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="D108" t="s">
-        <v>592</v>
-      </c>
-      <c r="F108" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="E108" t="s">
+        <v>371</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>504</v>
+      </c>
       <c r="I108" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
@@ -4713,17 +4776,17 @@
         <v>13</v>
       </c>
       <c r="B109">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D109" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F109" s="2"/>
       <c r="I109" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
@@ -4731,22 +4794,17 @@
         <v>13</v>
       </c>
       <c r="B110">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>112</v>
+        <v>584</v>
       </c>
       <c r="D110" t="s">
-        <v>247</v>
-      </c>
-      <c r="E110" t="s">
-        <v>247</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>506</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="F110" s="2"/>
       <c r="I110" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
@@ -4754,22 +4812,22 @@
         <v>13</v>
       </c>
       <c r="B111">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D111" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E111" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="I111" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
@@ -4777,22 +4835,22 @@
         <v>13</v>
       </c>
       <c r="B112">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C112" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D112" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E112" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="I112" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
@@ -4800,17 +4858,22 @@
         <v>13</v>
       </c>
       <c r="B113">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C113" t="s">
-        <v>586</v>
+        <v>113</v>
       </c>
       <c r="D113" t="s">
-        <v>598</v>
-      </c>
-      <c r="F113" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="E113" t="s">
+        <v>248</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>507</v>
+      </c>
       <c r="I113" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
@@ -4818,17 +4881,17 @@
         <v>13</v>
       </c>
       <c r="B114">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D114" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="F114" s="2"/>
       <c r="I114" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
@@ -4836,17 +4899,17 @@
         <v>13</v>
       </c>
       <c r="B115">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C115" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D115" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F115" s="2"/>
       <c r="I115" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
@@ -4854,17 +4917,17 @@
         <v>13</v>
       </c>
       <c r="B116">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C116" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D116" t="s">
         <v>590</v>
       </c>
       <c r="F116" s="2"/>
       <c r="I116" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
@@ -4872,17 +4935,17 @@
         <v>13</v>
       </c>
       <c r="B117">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C117" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="D117" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="F117" s="2"/>
       <c r="I117" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
@@ -4890,17 +4953,17 @@
         <v>13</v>
       </c>
       <c r="B118">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C118" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D118" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F118" s="2"/>
       <c r="I118" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
@@ -4908,17 +4971,17 @@
         <v>13</v>
       </c>
       <c r="B119">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C119" t="s">
-        <v>577</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>595</v>
+        <v>575</v>
+      </c>
+      <c r="D119" t="s">
+        <v>596</v>
       </c>
       <c r="F119" s="2"/>
       <c r="I119" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
@@ -4926,17 +4989,17 @@
         <v>13</v>
       </c>
       <c r="B120">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C120" t="s">
-        <v>578</v>
-      </c>
-      <c r="D120" t="s">
+        <v>576</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>594</v>
       </c>
       <c r="F120" s="2"/>
       <c r="I120" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
@@ -4944,17 +5007,17 @@
         <v>13</v>
       </c>
       <c r="B121">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C121" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D121" t="s">
         <v>593</v>
       </c>
       <c r="F121" s="2"/>
       <c r="I121" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
@@ -4962,40 +5025,35 @@
         <v>13</v>
       </c>
       <c r="B122">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D122" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F122" s="2"/>
       <c r="I122" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>115</v>
+        <v>582</v>
       </c>
       <c r="D123" t="s">
-        <v>250</v>
-      </c>
-      <c r="E123" t="s">
-        <v>373</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>509</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="F123" s="2"/>
       <c r="I123" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
@@ -5003,22 +5061,22 @@
         <v>14</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E124" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I124" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
@@ -5026,22 +5084,22 @@
         <v>14</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D125" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E125" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="I125" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
@@ -5049,22 +5107,22 @@
         <v>14</v>
       </c>
       <c r="B126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C126" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D126" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E126" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I126" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
@@ -5072,22 +5130,22 @@
         <v>14</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D127" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E127" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="I127" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
@@ -5095,22 +5153,22 @@
         <v>14</v>
       </c>
       <c r="B128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D128" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E128" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="I128" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -5118,19 +5176,22 @@
         <v>14</v>
       </c>
       <c r="B129">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C129" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D129" t="s">
-        <v>549</v>
+        <v>254</v>
+      </c>
+      <c r="E129" t="s">
+        <v>377</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I129" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
@@ -5138,22 +5199,19 @@
         <v>14</v>
       </c>
       <c r="B130">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D130" t="s">
-        <v>256</v>
-      </c>
-      <c r="E130" t="s">
-        <v>379</v>
+        <v>548</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I130" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
@@ -5161,22 +5219,22 @@
         <v>14</v>
       </c>
       <c r="B131">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D131" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E131" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I131" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
@@ -5184,22 +5242,22 @@
         <v>14</v>
       </c>
       <c r="B132">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D132" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E132" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I132" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
@@ -5207,22 +5265,22 @@
         <v>14</v>
       </c>
       <c r="B133">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C133" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D133" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E133" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="I133" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
@@ -5230,22 +5288,22 @@
         <v>14</v>
       </c>
       <c r="B134">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D134" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E134" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I134" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
@@ -5253,91 +5311,75 @@
         <v>14</v>
       </c>
       <c r="B135">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C135" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D135" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E135" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I135" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>128</v>
+        <v>599</v>
       </c>
       <c r="D136" t="s">
-        <v>262</v>
-      </c>
-      <c r="E136" t="s">
-        <v>385</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="I136" t="s">
-        <v>546</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="F136" s="2"/>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>129</v>
+        <v>600</v>
       </c>
       <c r="D137" t="s">
-        <v>263</v>
-      </c>
-      <c r="E137" t="s">
-        <v>386</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="I137" t="s">
-        <v>546</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="F137" s="2"/>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
+        <v>14</v>
+      </c>
+      <c r="B138">
         <v>15</v>
       </c>
-      <c r="B138">
-        <v>3</v>
-      </c>
       <c r="C138" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D138" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E138" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I138" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
@@ -5345,22 +5387,22 @@
         <v>15</v>
       </c>
       <c r="B139">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D139" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E139" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="I139" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
@@ -5368,22 +5410,22 @@
         <v>15</v>
       </c>
       <c r="B140">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C140" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D140" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E140" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I140" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
@@ -5391,22 +5433,22 @@
         <v>15</v>
       </c>
       <c r="B141">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D141" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E141" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="I141" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
@@ -5414,428 +5456,568 @@
         <v>15</v>
       </c>
       <c r="B142">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D142" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E142" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="I142" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C143" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D143" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E143" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="I143" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C144" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D144" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E144" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="I144" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C145" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D145" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E145" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I145" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B146">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C146" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D146" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E146" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="I146" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B147">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C147" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D147" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E147" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I147" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B148">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C148" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D148" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I148" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B149">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D149" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E149" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="I149" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B150">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C150" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D150" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E150" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="I150" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B151">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C151" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D151" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E151" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="I151" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B152">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C152" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D152" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E152" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="I152" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" ht="15">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B153">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>145</v>
+        <v>602</v>
       </c>
       <c r="D153" t="s">
-        <v>279</v>
-      </c>
-      <c r="E153" t="s">
-        <v>402</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="I153" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" ht="15">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B154">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C154" t="s">
-        <v>146</v>
+        <v>606</v>
       </c>
       <c r="D154" t="s">
-        <v>280</v>
-      </c>
-      <c r="E154" t="s">
-        <v>403</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="I154" t="s">
-        <v>546</v>
+        <v>613</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B155">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C155" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D155" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E155" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="I155" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B156">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>573</v>
+        <v>142</v>
       </c>
       <c r="D156" t="s">
-        <v>574</v>
-      </c>
-      <c r="F156" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E156" t="s">
+        <v>399</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="I156" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B157">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C157" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D157" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E157" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="I157" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B158">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D158" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E158" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="I158" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="B159">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D159" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E159" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="I159" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
+        <v>607</v>
+      </c>
+      <c r="B160">
+        <v>15</v>
+      </c>
+      <c r="C160" t="s">
+        <v>146</v>
+      </c>
+      <c r="D160" t="s">
+        <v>280</v>
+      </c>
+      <c r="E160" t="s">
+        <v>403</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I160" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>607</v>
+      </c>
+      <c r="B161">
         <v>16</v>
       </c>
-      <c r="B160">
+      <c r="C161" t="s">
+        <v>601</v>
+      </c>
+      <c r="D161" t="s">
+        <v>609</v>
+      </c>
+      <c r="F161" s="2"/>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>607</v>
+      </c>
+      <c r="B162">
+        <v>17</v>
+      </c>
+      <c r="C162" t="s">
+        <v>572</v>
+      </c>
+      <c r="D162" t="s">
+        <v>573</v>
+      </c>
+      <c r="F162" s="2"/>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>607</v>
+      </c>
+      <c r="B163">
         <v>18</v>
       </c>
-      <c r="C160" t="s">
-        <v>151</v>
-      </c>
-      <c r="D160" t="s">
-        <v>285</v>
-      </c>
-      <c r="E160" t="s">
-        <v>408</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="I160" t="s">
-        <v>546</v>
+      <c r="C163" t="s">
+        <v>147</v>
+      </c>
+      <c r="D163" t="s">
+        <v>281</v>
+      </c>
+      <c r="E163" t="s">
+        <v>404</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="I163" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>607</v>
+      </c>
+      <c r="B164">
+        <v>19</v>
+      </c>
+      <c r="C164" t="s">
+        <v>148</v>
+      </c>
+      <c r="D164" t="s">
+        <v>282</v>
+      </c>
+      <c r="E164" t="s">
+        <v>405</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="I164" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>607</v>
+      </c>
+      <c r="B165">
+        <v>20</v>
+      </c>
+      <c r="C165" t="s">
+        <v>149</v>
+      </c>
+      <c r="D165" t="s">
+        <v>283</v>
+      </c>
+      <c r="E165" t="s">
+        <v>406</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I165" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>607</v>
+      </c>
+      <c r="B166">
+        <v>21</v>
+      </c>
+      <c r="C166" t="s">
+        <v>150</v>
+      </c>
+      <c r="D166" t="s">
+        <v>284</v>
+      </c>
+      <c r="E166" t="s">
+        <v>407</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I166" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>607</v>
+      </c>
+      <c r="B167">
+        <v>22</v>
+      </c>
+      <c r="C167" t="s">
+        <v>604</v>
+      </c>
+      <c r="D167" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>607</v>
+      </c>
+      <c r="B168">
+        <v>23</v>
+      </c>
+      <c r="C168" t="s">
+        <v>605</v>
+      </c>
+      <c r="D168" t="s">
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -5915,69 +6097,69 @@
     <hyperlink ref="F82" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
     <hyperlink ref="F83" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
     <hyperlink ref="F84" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F85" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F86" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F87" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F88" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="F89" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F90" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F91" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F92" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F93" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F94" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F95" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F96" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F97" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="F98" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="F99" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="F100" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="F101" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="F102" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="F103" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="F104" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="F105" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="F106" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="F107" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="F110" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="F111" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="F112" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="F123" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="F124" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="F125" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="F126" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="F127" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="F128" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="F129" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="F130" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="F131" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="F132" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="F133" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="F134" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="F135" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="F136" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="F137" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="F138" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="F139" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="F140" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="F141" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="F142" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="F143" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="F144" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="F145" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="F146" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="F147" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="F148" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="F149" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F150" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="F151" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="F152" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="F153" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="F154" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F155" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="F157" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="F158" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="F159" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="F160" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="F86" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F87" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F88" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F89" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F90" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F91" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F92" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F93" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F94" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="F95" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F96" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F97" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F98" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="F99" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F100" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="F101" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F102" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F103" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F104" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F105" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F106" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="F107" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F108" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="F111" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="F112" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="F113" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F124" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="F125" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F126" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="F127" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F128" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="F129" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F130" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="F131" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F132" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="F133" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F134" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="F135" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F138" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="F139" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="F140" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="F141" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="F142" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="F143" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="F144" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="F145" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="F146" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="F147" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="F148" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="F149" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="F150" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="F151" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F152" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="F155" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="F156" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="F157" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="F158" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="F159" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="F160" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="F163" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="F164" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="F165" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="F166" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
     <hyperlink ref="F39" r:id="rId138" xr:uid="{BE4A9F9B-8C1C-429F-B84F-4D7FD81CAD0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Onedrive\CV\dm-dut.github.io\paper-monitor\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0EB9C8-C617-445B-A51D-83EB4CB191E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58C7A2C-3751-4759-A289-59B3FCBE7EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="617">
   <si>
     <t>Category</t>
   </si>
@@ -1927,6 +1927,14 @@
   </si>
   <si>
     <t>1387-3326</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Naval Research Logistics</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0894-069X</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2323,14 +2331,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J168"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:J169"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.08984375" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
     <col min="3" max="3" width="83" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" customWidth="1"/>
-    <col min="6" max="6" width="59.36328125" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="59.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4241,6 +4249,9 @@
         <v>614</v>
       </c>
       <c r="F85" s="2"/>
+      <c r="I85" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
@@ -5343,6 +5354,9 @@
         <v>598</v>
       </c>
       <c r="F136" s="2"/>
+      <c r="I136" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
@@ -5358,6 +5372,9 @@
         <v>608</v>
       </c>
       <c r="F137" s="2"/>
+      <c r="I137" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
@@ -5620,17 +5637,12 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>137</v>
+        <v>615</v>
       </c>
       <c r="D149" t="s">
-        <v>271</v>
-      </c>
-      <c r="E149" t="s">
-        <v>394</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>531</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="F149" s="2"/>
       <c r="I149" t="s">
         <v>545</v>
       </c>
@@ -5643,16 +5655,16 @@
         <v>5</v>
       </c>
       <c r="C150" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D150" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E150" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I150" t="s">
         <v>545</v>
@@ -5666,16 +5678,16 @@
         <v>6</v>
       </c>
       <c r="C151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D151" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E151" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I151" t="s">
         <v>545</v>
@@ -5689,22 +5701,22 @@
         <v>7</v>
       </c>
       <c r="C152" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D152" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E152" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I152" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
         <v>607</v>
       </c>
@@ -5712,10 +5724,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>602</v>
+        <v>140</v>
       </c>
       <c r="D153" t="s">
-        <v>612</v>
+        <v>274</v>
+      </c>
+      <c r="E153" t="s">
+        <v>397</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="I153" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -5726,13 +5747,16 @@
         <v>9</v>
       </c>
       <c r="C154" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="D154" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" ht="15">
+        <v>612</v>
+      </c>
+      <c r="I154" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" t="s">
         <v>607</v>
       </c>
@@ -5740,16 +5764,10 @@
         <v>10</v>
       </c>
       <c r="C155" t="s">
-        <v>141</v>
+        <v>606</v>
       </c>
       <c r="D155" t="s">
-        <v>275</v>
-      </c>
-      <c r="E155" t="s">
-        <v>398</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>535</v>
+        <v>613</v>
       </c>
       <c r="I155" t="s">
         <v>545</v>
@@ -5763,16 +5781,16 @@
         <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D156" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E156" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I156" t="s">
         <v>545</v>
@@ -5786,16 +5804,16 @@
         <v>12</v>
       </c>
       <c r="C157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D157" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E157" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I157" t="s">
         <v>545</v>
@@ -5809,16 +5827,16 @@
         <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E158" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I158" t="s">
         <v>545</v>
@@ -5832,16 +5850,16 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D159" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E159" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I159" t="s">
         <v>545</v>
@@ -5855,16 +5873,16 @@
         <v>15</v>
       </c>
       <c r="C160" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D160" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E160" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I160" t="s">
         <v>545</v>
@@ -5878,12 +5896,20 @@
         <v>16</v>
       </c>
       <c r="C161" t="s">
-        <v>601</v>
+        <v>146</v>
       </c>
       <c r="D161" t="s">
-        <v>609</v>
-      </c>
-      <c r="F161" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="E161" t="s">
+        <v>403</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I161" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
@@ -5893,12 +5919,15 @@
         <v>17</v>
       </c>
       <c r="C162" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
       <c r="D162" t="s">
-        <v>573</v>
+        <v>609</v>
       </c>
       <c r="F162" s="2"/>
+      <c r="I162" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
@@ -5908,17 +5937,12 @@
         <v>18</v>
       </c>
       <c r="C163" t="s">
-        <v>147</v>
+        <v>572</v>
       </c>
       <c r="D163" t="s">
-        <v>281</v>
-      </c>
-      <c r="E163" t="s">
-        <v>404</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>541</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="F163" s="2"/>
       <c r="I163" t="s">
         <v>545</v>
       </c>
@@ -5931,16 +5955,16 @@
         <v>19</v>
       </c>
       <c r="C164" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D164" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E164" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I164" t="s">
         <v>545</v>
@@ -5954,16 +5978,16 @@
         <v>20</v>
       </c>
       <c r="C165" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D165" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E165" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I165" t="s">
         <v>545</v>
@@ -5977,22 +6001,22 @@
         <v>21</v>
       </c>
       <c r="C166" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E166" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I166" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
         <v>607</v>
       </c>
@@ -6000,10 +6024,19 @@
         <v>22</v>
       </c>
       <c r="C167" t="s">
-        <v>604</v>
+        <v>150</v>
       </c>
       <c r="D167" t="s">
-        <v>610</v>
+        <v>284</v>
+      </c>
+      <c r="E167" t="s">
+        <v>407</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I167" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -6014,10 +6047,30 @@
         <v>23</v>
       </c>
       <c r="C168" t="s">
+        <v>604</v>
+      </c>
+      <c r="D168" t="s">
+        <v>610</v>
+      </c>
+      <c r="I168" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>607</v>
+      </c>
+      <c r="B169">
+        <v>24</v>
+      </c>
+      <c r="C169" t="s">
         <v>605</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D169" t="s">
         <v>611</v>
+      </c>
+      <c r="I169" t="s">
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -6146,20 +6199,20 @@
     <hyperlink ref="F146" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
     <hyperlink ref="F147" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
     <hyperlink ref="F148" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="F149" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="F150" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="F151" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="F152" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F155" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="F156" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="F157" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="F158" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="F159" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F160" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="F163" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="F164" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="F165" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="F166" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="F150" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="F151" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="F152" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F153" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="F156" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="F157" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="F158" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="F159" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="F160" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="F161" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="F164" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="F165" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="F166" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="F167" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
     <hyperlink ref="F39" r:id="rId138" xr:uid="{BE4A9F9B-8C1C-429F-B84F-4D7FD81CAD0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E62FCEB5-5C95-4266-A548-4FBEEBA3A4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282D7EFE-460E-4CE1-884F-396C2499823A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="639">
   <si>
     <t>Category</t>
   </si>
@@ -1996,6 +1996,18 @@
   </si>
   <si>
     <t>Journal of Hospitality and Tourism Research</t>
+  </si>
+  <si>
+    <t>Others</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Patterns</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2666-3899</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2408,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.109375" style="2" customWidth="1"/>
@@ -6161,10 +6173,10 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" s="2" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="B170" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>147</v>
@@ -6184,10 +6196,10 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" s="2" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="B171" s="2">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>148</v>
@@ -6207,10 +6219,10 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" s="2" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="B172" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>149</v>
@@ -6230,10 +6242,10 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="2" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="B173" s="2">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>603</v>
@@ -6247,10 +6259,10 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="2" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="B174" s="2">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>604</v>
@@ -6264,10 +6276,10 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="2" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="B175" s="2">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>623</v>
@@ -6284,10 +6296,10 @@
     </row>
     <row r="176" spans="1:9" s="5" customFormat="1">
       <c r="A176" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="B176" s="5">
-        <v>26</v>
+        <v>636</v>
+      </c>
+      <c r="B176" s="2">
+        <v>7</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>626</v>
@@ -6297,6 +6309,26 @@
       </c>
       <c r="E176" s="5" t="s">
         <v>628</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B177" s="2">
+        <v>8</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/paper-monitor/config/journals.xlsx
+++ b/paper-monitor/config/journals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\paper-monitor\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282D7EFE-460E-4CE1-884F-396C2499823A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B359BC-62EC-4469-86E2-997FA7BCFD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1895,10 +1895,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Wiley/Taylor/WorldSci/Emerald</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>1536-9323</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2007,6 +2003,10 @@
   </si>
   <si>
     <t>2666-3899</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wiley/Taylor</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3580,13 +3580,13 @@
         <v>51</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="F52" s="3"/>
       <c r="I52" s="2" t="s">
@@ -3923,7 +3923,7 @@
         <v>15</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>204</v>
@@ -3969,13 +3969,13 @@
         <v>17</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="F69" s="3"/>
       <c r="I69" s="2" t="s">
@@ -3990,13 +3990,13 @@
         <v>18</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="F70" s="3"/>
       <c r="I70" s="2" t="s">
@@ -4011,13 +4011,13 @@
         <v>19</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="F71" s="3"/>
       <c r="I71" s="2" t="s">
@@ -4032,7 +4032,7 @@
         <v>20</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>197</v>
@@ -4447,7 +4447,7 @@
         <v>602</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F90" s="3"/>
       <c r="I90" s="2" t="s">
@@ -5570,7 +5570,7 @@
         <v>599</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F142" s="3"/>
       <c r="I142" s="2" t="s">
@@ -5763,7 +5763,7 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B151" s="2">
         <v>1</v>
@@ -5786,7 +5786,7 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B152" s="2">
         <v>2</v>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B153" s="2">
         <v>3</v>
@@ -5832,16 +5832,16 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B154" s="2">
         <v>4</v>
       </c>
       <c r="C154" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="F154" s="3"/>
       <c r="I154" s="2" t="s">
@@ -5850,7 +5850,7 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B155" s="2">
         <v>5</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B156" s="2">
         <v>6</v>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B157" s="2">
         <v>7</v>
@@ -5919,7 +5919,7 @@
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B158" s="2">
         <v>8</v>
@@ -5942,7 +5942,7 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B159" s="2">
         <v>9</v>
@@ -5951,7 +5951,7 @@
         <v>601</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>544</v>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="160" spans="1:9">
       <c r="A160" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B160" s="2">
         <v>10</v>
@@ -5968,7 +5968,7 @@
         <v>605</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="I160" s="2" t="s">
         <v>544</v>
@@ -5976,7 +5976,7 @@
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B161" s="2">
         <v>11</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B162" s="2">
         <v>12</v>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B163" s="2">
         <v>13</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B164" s="2">
         <v>14</v>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B165" s="2">
         <v>15</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B166" s="2">
         <v>16</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B167" s="2">
         <v>17</v>
@@ -6123,7 +6123,7 @@
         <v>600</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F167" s="3"/>
       <c r="I167" s="2" t="s">
@@ -6132,7 +6132,7 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B168" s="2">
         <v>18</v>
@@ -6150,7 +6150,7 @@
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B169" s="2">
         <v>19</v>
@@ -6173,7 +6173,7 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B170" s="2">
         <v>1</v>
@@ -6196,7 +6196,7 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B171" s="2">
         <v>2</v>
@@ -6219,7 +6219,7 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B172" s="2">
         <v>3</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B173" s="2">
         <v>4</v>
@@ -6251,7 +6251,7 @@
         <v>603</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I173" s="2" t="s">
         <v>544</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B174" s="2">
         <v>5</v>
@@ -6268,7 +6268,7 @@
         <v>604</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I174" s="2" t="s">
         <v>544</v>
@@ -6276,19 +6276,19 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B175" s="2">
         <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D175" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="E175" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="I175" s="2" t="s">
         <v>544</v>
@@ -6296,19 +6296,19 @@
     </row>
     <row r="176" spans="1:9" s="5" customFormat="1">
       <c r="A176" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B176" s="2">
         <v>7</v>
       </c>
       <c r="C176" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="D176" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="D176" s="5" t="s">
+      <c r="E176" s="5" t="s">
         <v>627</v>
-      </c>
-      <c r="E176" s="5" t="s">
-        <v>628</v>
       </c>
       <c r="I176" s="2" t="s">
         <v>544</v>
@@ -6316,16 +6316,16 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B177" s="2">
         <v>8</v>
       </c>
       <c r="C177" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="D177" s="5" t="s">
         <v>637</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>638</v>
       </c>
       <c r="I177" s="2" t="s">
         <v>544</v>
